--- a/public/uploads/excel/product-excel-export.xlsx
+++ b/public/uploads/excel/product-excel-export.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2936">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="3136">
   <si>
     <t>Producto</t>
   </si>
@@ -1484,7 +1484,7 @@
     <t>235'8237</t>
   </si>
   <si>
-    <t>IM830</t>
+    <t>235'8351</t>
   </si>
   <si>
     <t>PLACA RECTIFICADORA</t>
@@ -2297,7 +2297,7 @@
     <t>0K50F-18-840</t>
   </si>
   <si>
-    <t>KW-408</t>
+    <t>HONGWIN</t>
   </si>
   <si>
     <t>VALVULA DEL MINIMO</t>
@@ -2861,7 +2861,7 @@
     <t>VALVULA DE PRESION</t>
   </si>
   <si>
-    <t>HONGWIN</t>
+    <t>NNISFFV0</t>
   </si>
   <si>
     <t>FUSIBLE 15 AMP</t>
@@ -8750,7 +8750,7 @@
     <t>RAGULADOR 12V</t>
   </si>
   <si>
-    <t>IH252VC</t>
+    <t>IH252</t>
   </si>
   <si>
     <t>66-9126</t>
@@ -8823,6 +8823,606 @@
   </si>
   <si>
     <t>CIB</t>
+  </si>
+  <si>
+    <t>GUM-34</t>
+  </si>
+  <si>
+    <t>23rd Mar, 2026</t>
+  </si>
+  <si>
+    <t>MB000948</t>
+  </si>
+  <si>
+    <t>ICHIBAN</t>
+  </si>
+  <si>
+    <t>CRU-10115</t>
+  </si>
+  <si>
+    <t>GUT-12</t>
+  </si>
+  <si>
+    <t>TN-134</t>
+  </si>
+  <si>
+    <t>TT-113</t>
+  </si>
+  <si>
+    <t>TT-112</t>
+  </si>
+  <si>
+    <t>TMZ-109</t>
+  </si>
+  <si>
+    <t>24th Mar, 2026</t>
+  </si>
+  <si>
+    <t>CRU-10044</t>
+  </si>
+  <si>
+    <t>T5-310X</t>
+  </si>
+  <si>
+    <t>TN-146</t>
+  </si>
+  <si>
+    <t>SA67-25-06XA</t>
+  </si>
+  <si>
+    <t>04371-04030</t>
+  </si>
+  <si>
+    <t>SA68-25-06XA</t>
+  </si>
+  <si>
+    <t>ACETAMINOFEN</t>
+  </si>
+  <si>
+    <t>72MXFOJ5</t>
+  </si>
+  <si>
+    <t>25th Mar, 2026</t>
+  </si>
+  <si>
+    <t>TT-129-1A</t>
+  </si>
+  <si>
+    <t>26th Mar, 2026</t>
+  </si>
+  <si>
+    <t>GUMZ-9</t>
+  </si>
+  <si>
+    <t>JND</t>
+  </si>
+  <si>
+    <t>201-15</t>
+  </si>
+  <si>
+    <t>11th Apr, 2026</t>
+  </si>
+  <si>
+    <t>SWITCH 2GOLPE 4PINES</t>
+  </si>
+  <si>
+    <t>251-027</t>
+  </si>
+  <si>
+    <t>231-8268</t>
+  </si>
+  <si>
+    <t>17th Apr, 2026</t>
+  </si>
+  <si>
+    <t>SENSOR DE LEVAS</t>
+  </si>
+  <si>
+    <t>39350-22600</t>
+  </si>
+  <si>
+    <t>25th Apr, 2026</t>
+  </si>
+  <si>
+    <t>BOMBA DE AGUA</t>
+  </si>
+  <si>
+    <t>25100-4X500</t>
+  </si>
+  <si>
+    <t>29th Apr, 2026</t>
+  </si>
+  <si>
+    <t>BUJE EJE TRASERO</t>
+  </si>
+  <si>
+    <t>55130-4D000</t>
+  </si>
+  <si>
+    <t>YULIM</t>
+  </si>
+  <si>
+    <t>2nd May, 2026</t>
+  </si>
+  <si>
+    <t>BUJE BARRA ESTABILIZADORA</t>
+  </si>
+  <si>
+    <t>KKY01-34-156A</t>
+  </si>
+  <si>
+    <t>GY</t>
+  </si>
+  <si>
+    <t>CAMPANA DE FRENO</t>
+  </si>
+  <si>
+    <t>58411-1R000</t>
+  </si>
+  <si>
+    <t>EMPAQUE TAPA VALVULA</t>
+  </si>
+  <si>
+    <t>22441-26003</t>
+  </si>
+  <si>
+    <t>RADIADOR</t>
+  </si>
+  <si>
+    <t>16400-0L431</t>
+  </si>
+  <si>
+    <t>SPARK</t>
+  </si>
+  <si>
+    <t>5th May, 2026</t>
+  </si>
+  <si>
+    <t>AMORTIGUADOR DELANTERO</t>
+  </si>
+  <si>
+    <t>344202 / 444103</t>
+  </si>
+  <si>
+    <t>27301-2B100</t>
+  </si>
+  <si>
+    <t>ORIGINAL HYUNDAI/KIA</t>
+  </si>
+  <si>
+    <t>7th May, 2026</t>
+  </si>
+  <si>
+    <t>BOMBA AUXILIAR CLUTCH</t>
+  </si>
+  <si>
+    <t>31470-52121</t>
+  </si>
+  <si>
+    <t>TAKASHI</t>
+  </si>
+  <si>
+    <t>13th May, 2026</t>
+  </si>
+  <si>
+    <t>CEPO 5 PINES</t>
+  </si>
+  <si>
+    <t>NPC:14248C</t>
+  </si>
+  <si>
+    <t>TOTALPARTS</t>
+  </si>
+  <si>
+    <t>CREMALLERA</t>
+  </si>
+  <si>
+    <t>44200-0K040</t>
+  </si>
+  <si>
+    <t>PERFECT</t>
+  </si>
+  <si>
+    <t>14th May, 2026</t>
+  </si>
+  <si>
+    <t>TACOS DE FRENO DELANTERO</t>
+  </si>
+  <si>
+    <t>04465-0K300</t>
+  </si>
+  <si>
+    <t>15330-21011</t>
+  </si>
+  <si>
+    <t>16th May, 2026</t>
+  </si>
+  <si>
+    <t>110-1100</t>
+  </si>
+  <si>
+    <t>TERMINAL DE DIRECCION</t>
+  </si>
+  <si>
+    <t>AISIN</t>
+  </si>
+  <si>
+    <t>25th May, 2026</t>
+  </si>
+  <si>
+    <t>26th May, 2026</t>
+  </si>
+  <si>
+    <t>ROTULA INFERIOR RH</t>
+  </si>
+  <si>
+    <t>BUJIA DE PEZ 2F</t>
+  </si>
+  <si>
+    <t>30th May, 2026</t>
+  </si>
+  <si>
+    <t>BUJIA H4</t>
+  </si>
+  <si>
+    <t>SELLO DE FRENO 1-1/8</t>
+  </si>
+  <si>
+    <t>SAIKEN</t>
+  </si>
+  <si>
+    <t>SELLO DE FRENO 7/8</t>
+  </si>
+  <si>
+    <t>GUIA DE CEPILLO</t>
+  </si>
+  <si>
+    <t>13561-0E011</t>
+  </si>
+  <si>
+    <t>2nd Jun, 2026</t>
+  </si>
+  <si>
+    <t>BOMBILLO DE FRENO TRASEROS R/L</t>
+  </si>
+  <si>
+    <t>47550'OK020</t>
+  </si>
+  <si>
+    <t>HASAKI</t>
+  </si>
+  <si>
+    <t>3rd Jun, 2026</t>
+  </si>
+  <si>
+    <t>DGP2748</t>
+  </si>
+  <si>
+    <t>SENSOR DE OXIGENO #2</t>
+  </si>
+  <si>
+    <t>6th Jun, 2026</t>
+  </si>
+  <si>
+    <t>MOTOR DE ARRANQUE 10D</t>
+  </si>
+  <si>
+    <t>243-15003</t>
+  </si>
+  <si>
+    <t>10th Jun, 2026</t>
+  </si>
+  <si>
+    <t>BALINERA</t>
+  </si>
+  <si>
+    <t>TPFKF2JV</t>
+  </si>
+  <si>
+    <t>15th Jun, 2026</t>
+  </si>
+  <si>
+    <t>DBEHKPUG</t>
+  </si>
+  <si>
+    <t>IC5N2IIA</t>
+  </si>
+  <si>
+    <t>KOYO</t>
+  </si>
+  <si>
+    <t>41741M60B000-000</t>
+  </si>
+  <si>
+    <t>CCS7NOAO</t>
+  </si>
+  <si>
+    <t>GD60IB6L</t>
+  </si>
+  <si>
+    <t>PBLWHR0Z</t>
+  </si>
+  <si>
+    <t>KQSLPHAX</t>
+  </si>
+  <si>
+    <t>ZUYKIQ7O</t>
+  </si>
+  <si>
+    <t>GJ3YULK1</t>
+  </si>
+  <si>
+    <t>SQ8XHYD1</t>
+  </si>
+  <si>
+    <t>16th Jun, 2026</t>
+  </si>
+  <si>
+    <t>3930022600 IG</t>
+  </si>
+  <si>
+    <t>N826GIKS</t>
+  </si>
+  <si>
+    <t>GCOABDIJ</t>
+  </si>
+  <si>
+    <t>17th Jun, 2026</t>
+  </si>
+  <si>
+    <t>GM7FZQF3</t>
+  </si>
+  <si>
+    <t>C2M4T1Y7</t>
+  </si>
+  <si>
+    <t>NTS</t>
+  </si>
+  <si>
+    <t>N93OYMKD</t>
+  </si>
+  <si>
+    <t>PFI</t>
+  </si>
+  <si>
+    <t>QJTW9VGR</t>
+  </si>
+  <si>
+    <t>1VRNUA8P</t>
+  </si>
+  <si>
+    <t>0MCZLRG8</t>
+  </si>
+  <si>
+    <t>ZCZGZJA3</t>
+  </si>
+  <si>
+    <t>KFB</t>
+  </si>
+  <si>
+    <t>EO6R1GPA</t>
+  </si>
+  <si>
+    <t>NBN</t>
+  </si>
+  <si>
+    <t>18th Jun, 2026</t>
+  </si>
+  <si>
+    <t>W4AQHKTX</t>
+  </si>
+  <si>
+    <t>Z0JTJM53</t>
+  </si>
+  <si>
+    <t>NACHI</t>
+  </si>
+  <si>
+    <t>YRJ8NVGN</t>
+  </si>
+  <si>
+    <t>FBJ</t>
+  </si>
+  <si>
+    <t>OSC3AEMT</t>
+  </si>
+  <si>
+    <t>QMXCABE8</t>
+  </si>
+  <si>
+    <t>EBI</t>
+  </si>
+  <si>
+    <t>2YN8RCLT</t>
+  </si>
+  <si>
+    <t>19th Jun, 2026</t>
+  </si>
+  <si>
+    <t>IX123C</t>
+  </si>
+  <si>
+    <t>20th Jun, 2026</t>
+  </si>
+  <si>
+    <t>IN6001C</t>
+  </si>
+  <si>
+    <t>T0UJBFB9</t>
+  </si>
+  <si>
+    <t>22nd Jun, 2026</t>
+  </si>
+  <si>
+    <t>KDF2ITXY</t>
+  </si>
+  <si>
+    <t>LAMHWZFR</t>
+  </si>
+  <si>
+    <t>CJQ9X2C4</t>
+  </si>
+  <si>
+    <t>HB8KJEDA</t>
+  </si>
+  <si>
+    <t>949100-3820</t>
+  </si>
+  <si>
+    <t>24th Jun, 2026</t>
+  </si>
+  <si>
+    <t>3935023500 IE</t>
+  </si>
+  <si>
+    <t>Q4EH9W0K</t>
+  </si>
+  <si>
+    <t>8Y0JPKHR</t>
+  </si>
+  <si>
+    <t>90919'05024</t>
+  </si>
+  <si>
+    <t>25th Jun, 2026</t>
+  </si>
+  <si>
+    <t>26th Jun, 2026</t>
+  </si>
+  <si>
+    <t>U4EJZDBR</t>
+  </si>
+  <si>
+    <t>2STAZROV</t>
+  </si>
+  <si>
+    <t>OWAY65DG</t>
+  </si>
+  <si>
+    <t>VINI</t>
+  </si>
+  <si>
+    <t>XXERUOFD</t>
+  </si>
+  <si>
+    <t>NBR</t>
+  </si>
+  <si>
+    <t>DTX6D9WZ</t>
+  </si>
+  <si>
+    <t>MS2UPYQL</t>
+  </si>
+  <si>
+    <t>HAHICQAM</t>
+  </si>
+  <si>
+    <t>IVPRD8SY</t>
+  </si>
+  <si>
+    <t>27th Jun, 2026</t>
+  </si>
+  <si>
+    <t>XNZFIKCH</t>
+  </si>
+  <si>
+    <t>0CN25HVB</t>
+  </si>
+  <si>
+    <t>23731-EC00A</t>
+  </si>
+  <si>
+    <t>6th Jul, 2026</t>
+  </si>
+  <si>
+    <t>39180'25300</t>
+  </si>
+  <si>
+    <t>39180-25200</t>
+  </si>
+  <si>
+    <t>7th Jul, 2026</t>
+  </si>
+  <si>
+    <t>LM12748</t>
+  </si>
+  <si>
+    <t>KMM</t>
+  </si>
+  <si>
+    <t>CY9FKJQH</t>
+  </si>
+  <si>
+    <t>DACYO86T</t>
+  </si>
+  <si>
+    <t>GBWH'032</t>
+  </si>
+  <si>
+    <t>DHUCF8FS</t>
+  </si>
+  <si>
+    <t>89462-20040</t>
+  </si>
+  <si>
+    <t>RKSE6312</t>
+  </si>
+  <si>
+    <t>9th Jul, 2026</t>
+  </si>
+  <si>
+    <t>15100-250</t>
+  </si>
+  <si>
+    <t>CJ4QKAVR</t>
+  </si>
+  <si>
+    <t>ARF4ALAC</t>
+  </si>
+  <si>
+    <t>GEACBXU5</t>
+  </si>
+  <si>
+    <t>WJB</t>
+  </si>
+  <si>
+    <t>QQ3WJQUC</t>
+  </si>
+  <si>
+    <t>P5MUSFAJ</t>
+  </si>
+  <si>
+    <t>GWRMWXSL</t>
+  </si>
+  <si>
+    <t>OKD13WYW</t>
+  </si>
+  <si>
+    <t>M9LJQX0K</t>
+  </si>
+  <si>
+    <t>BALINERA CON SEGURO</t>
+  </si>
+  <si>
+    <t>FILTRO DE AIRE/CABINA</t>
+  </si>
+  <si>
+    <t>SENSOR DE GOLPE</t>
+  </si>
+  <si>
+    <t>89615-52030</t>
+  </si>
+  <si>
+    <t>LHUXSWCC</t>
+  </si>
+  <si>
+    <t>10th Jul, 2026</t>
+  </si>
+  <si>
+    <t>7GABSAJA</t>
+  </si>
+  <si>
+    <t>KWSM2A9B</t>
   </si>
 </sst>
 </file>
@@ -9162,7 +9762,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:G2228"/>
+  <dimension ref="A1:G2379"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="17.08" customWidth="true" style="0"/>
@@ -9329,7 +9929,7 @@
         <v>10</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7" t="s">
         <v>11</v>
@@ -9490,7 +10090,7 @@
         <v>10</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G14" t="s">
         <v>11</v>
@@ -9881,7 +10481,7 @@
         <v>10</v>
       </c>
       <c r="F31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G31" t="s">
         <v>11</v>
@@ -9973,7 +10573,7 @@
         <v>46</v>
       </c>
       <c r="F35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G35" t="s">
         <v>50</v>
@@ -10088,7 +10688,7 @@
         <v>46</v>
       </c>
       <c r="F40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G40" t="s">
         <v>50</v>
@@ -10249,7 +10849,7 @@
         <v>46</v>
       </c>
       <c r="F47">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G47" t="s">
         <v>72</v>
@@ -10295,7 +10895,7 @@
         <v>46</v>
       </c>
       <c r="F49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G49" t="s">
         <v>72</v>
@@ -10341,7 +10941,7 @@
         <v>46</v>
       </c>
       <c r="F51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G51" t="s">
         <v>72</v>
@@ -10387,7 +10987,7 @@
         <v>46</v>
       </c>
       <c r="F53">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G53" t="s">
         <v>86</v>
@@ -16321,7 +16921,7 @@
         <v>46</v>
       </c>
       <c r="F311">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G311" t="s">
         <v>160</v>
@@ -16643,7 +17243,7 @@
         <v>46</v>
       </c>
       <c r="F325">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G325" t="s">
         <v>179</v>
@@ -17172,7 +17772,7 @@
         <v>46</v>
       </c>
       <c r="F348">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G348" t="s">
         <v>212</v>
@@ -17218,7 +17818,7 @@
         <v>46</v>
       </c>
       <c r="F350">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G350" t="s">
         <v>212</v>
@@ -17379,7 +17979,7 @@
         <v>46</v>
       </c>
       <c r="F357">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G357" t="s">
         <v>212</v>
@@ -17494,7 +18094,7 @@
         <v>46</v>
       </c>
       <c r="F362">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G362" t="s">
         <v>212</v>
@@ -17908,7 +18508,7 @@
         <v>46</v>
       </c>
       <c r="F380">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="G380" t="s">
         <v>267</v>
@@ -17931,7 +18531,7 @@
         <v>46</v>
       </c>
       <c r="F381">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G381" t="s">
         <v>267</v>
@@ -18000,7 +18600,7 @@
         <v>46</v>
       </c>
       <c r="F384">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G384" t="s">
         <v>267</v>
@@ -18109,13 +18709,13 @@
         <v>266</v>
       </c>
       <c r="D389">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="E389" t="s">
         <v>46</v>
       </c>
       <c r="F389">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G389" t="s">
         <v>276</v>
@@ -18138,7 +18738,7 @@
         <v>46</v>
       </c>
       <c r="F390">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G390" t="s">
         <v>276</v>
@@ -18161,7 +18761,7 @@
         <v>46</v>
       </c>
       <c r="F391">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G391" t="s">
         <v>276</v>
@@ -18368,7 +18968,7 @@
         <v>46</v>
       </c>
       <c r="F400">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G400" t="s">
         <v>276</v>
@@ -18414,7 +19014,7 @@
         <v>46</v>
       </c>
       <c r="F402">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G402" t="s">
         <v>276</v>
@@ -18483,7 +19083,7 @@
         <v>46</v>
       </c>
       <c r="F405">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G405" t="s">
         <v>276</v>
@@ -18598,7 +19198,7 @@
         <v>46</v>
       </c>
       <c r="F410">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G410" t="s">
         <v>276</v>
@@ -18644,7 +19244,7 @@
         <v>46</v>
       </c>
       <c r="F412">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G412" t="s">
         <v>276</v>
@@ -18943,7 +19543,7 @@
         <v>46</v>
       </c>
       <c r="F425">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G425" t="s">
         <v>311</v>
@@ -19449,7 +20049,7 @@
         <v>46</v>
       </c>
       <c r="F447">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G447" t="s">
         <v>332</v>
@@ -19840,7 +20440,7 @@
         <v>46</v>
       </c>
       <c r="F464">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G464" t="s">
         <v>355</v>
@@ -20024,7 +20624,7 @@
         <v>46</v>
       </c>
       <c r="F472">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G472" t="s">
         <v>367</v>
@@ -20093,7 +20693,7 @@
         <v>46</v>
       </c>
       <c r="F475">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G475" t="s">
         <v>367</v>
@@ -20231,7 +20831,7 @@
         <v>46</v>
       </c>
       <c r="F481">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G481" t="s">
         <v>367</v>
@@ -20576,7 +21176,7 @@
         <v>46</v>
       </c>
       <c r="F496">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G496" t="s">
         <v>367</v>
@@ -20898,7 +21498,7 @@
         <v>46</v>
       </c>
       <c r="F510">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G510" t="s">
         <v>389</v>
@@ -21703,7 +22303,7 @@
         <v>46</v>
       </c>
       <c r="F545">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G545" t="s">
         <v>431</v>
@@ -21956,7 +22556,7 @@
         <v>46</v>
       </c>
       <c r="F556">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G556" t="s">
         <v>443</v>
@@ -22048,7 +22648,7 @@
         <v>46</v>
       </c>
       <c r="F560">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G560" t="s">
         <v>443</v>
@@ -22117,7 +22717,7 @@
         <v>46</v>
       </c>
       <c r="F563">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G563" t="s">
         <v>448</v>
@@ -22623,7 +23223,7 @@
         <v>46</v>
       </c>
       <c r="F585">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G585" t="s">
         <v>448</v>
@@ -23031,13 +23631,13 @@
         <v>83</v>
       </c>
       <c r="D603">
-        <v>1200</v>
+        <v>1450</v>
       </c>
       <c r="E603" t="s">
         <v>46</v>
       </c>
       <c r="F603">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G603" t="s">
         <v>476</v>
@@ -23051,7 +23651,7 @@
         <v>489</v>
       </c>
       <c r="C604" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="D604">
         <v>1400</v>
@@ -23060,7 +23660,7 @@
         <v>46</v>
       </c>
       <c r="F604">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G604" t="s">
         <v>476</v>
@@ -23267,7 +23867,7 @@
         <v>46</v>
       </c>
       <c r="F613">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G613" t="s">
         <v>476</v>
@@ -23290,7 +23890,7 @@
         <v>46</v>
       </c>
       <c r="F614">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G614" t="s">
         <v>476</v>
@@ -23399,13 +23999,13 @@
         <v>83</v>
       </c>
       <c r="D619">
-        <v>950</v>
+        <v>1100</v>
       </c>
       <c r="E619" t="s">
         <v>46</v>
       </c>
       <c r="F619">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G619" t="s">
         <v>504</v>
@@ -23428,7 +24028,7 @@
         <v>46</v>
       </c>
       <c r="F620">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G620" t="s">
         <v>504</v>
@@ -23497,7 +24097,7 @@
         <v>46</v>
       </c>
       <c r="F623">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="G623" t="s">
         <v>514</v>
@@ -23882,13 +24482,13 @@
         <v>278</v>
       </c>
       <c r="D640">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="E640" t="s">
         <v>46</v>
       </c>
       <c r="F640">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G640" t="s">
         <v>523</v>
@@ -23911,7 +24511,7 @@
         <v>46</v>
       </c>
       <c r="F641">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G641" t="s">
         <v>523</v>
@@ -24003,7 +24603,7 @@
         <v>46</v>
       </c>
       <c r="F645">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G645" t="s">
         <v>523</v>
@@ -24095,7 +24695,7 @@
         <v>46</v>
       </c>
       <c r="F649">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G649" t="s">
         <v>523</v>
@@ -24210,7 +24810,7 @@
         <v>46</v>
       </c>
       <c r="F654">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G654" t="s">
         <v>523</v>
@@ -24233,7 +24833,7 @@
         <v>46</v>
       </c>
       <c r="F655">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G655" t="s">
         <v>523</v>
@@ -24256,7 +24856,7 @@
         <v>46</v>
       </c>
       <c r="F656">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G656" t="s">
         <v>523</v>
@@ -24279,7 +24879,7 @@
         <v>46</v>
       </c>
       <c r="F657">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G657" t="s">
         <v>523</v>
@@ -24785,7 +25385,7 @@
         <v>46</v>
       </c>
       <c r="F679">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G679" t="s">
         <v>572</v>
@@ -24831,7 +25431,7 @@
         <v>46</v>
       </c>
       <c r="F681">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G681" t="s">
         <v>572</v>
@@ -25751,7 +26351,7 @@
         <v>46</v>
       </c>
       <c r="F721">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G721" t="s">
         <v>601</v>
@@ -26970,7 +27570,7 @@
         <v>46</v>
       </c>
       <c r="F774">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G774" t="s">
         <v>623</v>
@@ -27200,7 +27800,7 @@
         <v>46</v>
       </c>
       <c r="F784">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G784" t="s">
         <v>657</v>
@@ -27723,13 +28323,13 @@
         <v>633</v>
       </c>
       <c r="D807">
-        <v>200</v>
+        <v>320</v>
       </c>
       <c r="E807" t="s">
         <v>46</v>
       </c>
       <c r="F807">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G807" t="s">
         <v>657</v>
@@ -27752,7 +28352,7 @@
         <v>46</v>
       </c>
       <c r="F808">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G808" t="s">
         <v>657</v>
@@ -28166,7 +28766,7 @@
         <v>46</v>
       </c>
       <c r="F826">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G826" t="s">
         <v>694</v>
@@ -28672,7 +29272,7 @@
         <v>46</v>
       </c>
       <c r="F848">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G848" t="s">
         <v>742</v>
@@ -28797,20 +29397,20 @@
       <c r="A854" t="s">
         <v>692</v>
       </c>
-      <c r="B854" t="s">
+      <c r="B854">
+        <v>1054303201594</v>
+      </c>
+      <c r="C854" t="s">
         <v>760</v>
       </c>
-      <c r="C854" t="s">
-        <v>712</v>
-      </c>
       <c r="D854">
-        <v>950</v>
+        <v>800</v>
       </c>
       <c r="E854" t="s">
         <v>46</v>
       </c>
       <c r="F854">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G854" t="s">
         <v>742</v>
@@ -29086,7 +29686,7 @@
         <v>46</v>
       </c>
       <c r="F866">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G866" t="s">
         <v>775</v>
@@ -29339,7 +29939,7 @@
         <v>46</v>
       </c>
       <c r="F877">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G877" t="s">
         <v>775</v>
@@ -29523,7 +30123,7 @@
         <v>46</v>
       </c>
       <c r="F885">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G885" t="s">
         <v>775</v>
@@ -29546,7 +30146,7 @@
         <v>46</v>
       </c>
       <c r="F886">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G886" t="s">
         <v>775</v>
@@ -29638,7 +30238,7 @@
         <v>46</v>
       </c>
       <c r="F890">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G890" t="s">
         <v>775</v>
@@ -30420,7 +31020,7 @@
         <v>46</v>
       </c>
       <c r="F924">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G924" t="s">
         <v>866</v>
@@ -30437,7 +31037,7 @@
         <v>767</v>
       </c>
       <c r="D925">
-        <v>850</v>
+        <v>950</v>
       </c>
       <c r="E925" t="s">
         <v>46</v>
@@ -30535,7 +31135,7 @@
         <v>46</v>
       </c>
       <c r="F929">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G929" t="s">
         <v>866</v>
@@ -31018,7 +31618,7 @@
         <v>46</v>
       </c>
       <c r="F950">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G950" t="s">
         <v>883</v>
@@ -31271,7 +31871,7 @@
         <v>46</v>
       </c>
       <c r="F961">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G961" t="s">
         <v>912</v>
@@ -31386,7 +31986,7 @@
         <v>46</v>
       </c>
       <c r="F966">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G966" t="s">
         <v>912</v>
@@ -31764,11 +32364,11 @@
       <c r="A983" t="s">
         <v>947</v>
       </c>
-      <c r="B983">
-        <v>5456156156</v>
+      <c r="B983" t="s">
+        <v>948</v>
       </c>
       <c r="C983" t="s">
-        <v>948</v>
+        <v>760</v>
       </c>
       <c r="D983">
         <v>2400</v>
@@ -31777,7 +32377,7 @@
         <v>46</v>
       </c>
       <c r="F983">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G983" t="s">
         <v>943</v>
@@ -31915,7 +32515,7 @@
         <v>46</v>
       </c>
       <c r="F989">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G989" t="s">
         <v>943</v>
@@ -32168,7 +32768,7 @@
         <v>46</v>
       </c>
       <c r="F1000">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G1000" t="s">
         <v>943</v>
@@ -32366,16 +32966,16 @@
         <v>984</v>
       </c>
       <c r="C1009" t="s">
-        <v>459</v>
+        <v>760</v>
       </c>
       <c r="D1009">
-        <v>1200</v>
+        <v>990</v>
       </c>
       <c r="E1009" t="s">
         <v>46</v>
       </c>
       <c r="F1009">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1009" t="s">
         <v>943</v>
@@ -32421,7 +33021,7 @@
         <v>46</v>
       </c>
       <c r="F1011">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G1011" t="s">
         <v>943</v>
@@ -32628,7 +33228,7 @@
         <v>46</v>
       </c>
       <c r="F1020">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1020" t="s">
         <v>987</v>
@@ -32881,7 +33481,7 @@
         <v>46</v>
       </c>
       <c r="F1031">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1031" t="s">
         <v>987</v>
@@ -32927,7 +33527,7 @@
         <v>46</v>
       </c>
       <c r="F1033">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1033" t="s">
         <v>987</v>
@@ -33180,7 +33780,7 @@
         <v>46</v>
       </c>
       <c r="F1044">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G1044" t="s">
         <v>987</v>
@@ -34054,7 +34654,7 @@
         <v>46</v>
       </c>
       <c r="F1082">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1082" t="s">
         <v>1081</v>
@@ -34514,7 +35114,7 @@
         <v>46</v>
       </c>
       <c r="F1102">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1102" t="s">
         <v>1109</v>
@@ -34652,7 +35252,7 @@
         <v>46</v>
       </c>
       <c r="F1108">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G1108" t="s">
         <v>1120</v>
@@ -35595,7 +36195,7 @@
         <v>46</v>
       </c>
       <c r="F1149">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1149" t="s">
         <v>1185</v>
@@ -35986,7 +36586,7 @@
         <v>46</v>
       </c>
       <c r="F1166">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G1166" t="s">
         <v>1185</v>
@@ -36032,7 +36632,7 @@
         <v>46</v>
       </c>
       <c r="F1168">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G1168" t="s">
         <v>1185</v>
@@ -36124,7 +36724,7 @@
         <v>46</v>
       </c>
       <c r="F1172">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1172" t="s">
         <v>1185</v>
@@ -36170,7 +36770,7 @@
         <v>46</v>
       </c>
       <c r="F1174">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G1174" t="s">
         <v>1185</v>
@@ -36285,7 +36885,7 @@
         <v>46</v>
       </c>
       <c r="F1179">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G1179" t="s">
         <v>1185</v>
@@ -36354,7 +36954,7 @@
         <v>46</v>
       </c>
       <c r="F1182">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1182" t="s">
         <v>1185</v>
@@ -37504,7 +38104,7 @@
         <v>46</v>
       </c>
       <c r="F1232">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G1232" t="s">
         <v>1348</v>
@@ -37573,7 +38173,7 @@
         <v>46</v>
       </c>
       <c r="F1235">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1235" t="s">
         <v>1348</v>
@@ -37826,7 +38426,7 @@
         <v>46</v>
       </c>
       <c r="F1246">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1246" t="s">
         <v>1348</v>
@@ -38493,7 +39093,7 @@
         <v>46</v>
       </c>
       <c r="F1275">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1275" t="s">
         <v>1348</v>
@@ -38585,7 +39185,7 @@
         <v>46</v>
       </c>
       <c r="F1279">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="G1279" t="s">
         <v>1348</v>
@@ -38631,7 +39231,7 @@
         <v>46</v>
       </c>
       <c r="F1281">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G1281" t="s">
         <v>1348</v>
@@ -38700,7 +39300,7 @@
         <v>46</v>
       </c>
       <c r="F1284">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1284" t="s">
         <v>1348</v>
@@ -38953,7 +39553,7 @@
         <v>46</v>
       </c>
       <c r="F1295">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G1295" t="s">
         <v>1348</v>
@@ -39022,7 +39622,7 @@
         <v>46</v>
       </c>
       <c r="F1298">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1298" t="s">
         <v>1348</v>
@@ -39068,7 +39668,7 @@
         <v>46</v>
       </c>
       <c r="F1300">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1300" t="s">
         <v>1348</v>
@@ -39367,7 +39967,7 @@
         <v>46</v>
       </c>
       <c r="F1313">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1313" t="s">
         <v>1348</v>
@@ -39850,7 +40450,7 @@
         <v>46</v>
       </c>
       <c r="F1334">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1334" t="s">
         <v>1541</v>
@@ -39896,7 +40496,7 @@
         <v>46</v>
       </c>
       <c r="F1336">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1336" t="s">
         <v>1541</v>
@@ -39942,7 +40542,7 @@
         <v>46</v>
       </c>
       <c r="F1338">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1338" t="s">
         <v>1559</v>
@@ -40839,7 +41439,7 @@
         <v>46</v>
       </c>
       <c r="F1377">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1377" t="s">
         <v>1575</v>
@@ -40931,7 +41531,7 @@
         <v>46</v>
       </c>
       <c r="F1381">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G1381" t="s">
         <v>1575</v>
@@ -40954,7 +41554,7 @@
         <v>46</v>
       </c>
       <c r="F1382">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1382" t="s">
         <v>1575</v>
@@ -41000,7 +41600,7 @@
         <v>46</v>
       </c>
       <c r="F1384">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G1384" t="s">
         <v>1575</v>
@@ -41230,7 +41830,7 @@
         <v>46</v>
       </c>
       <c r="F1394">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G1394" t="s">
         <v>1575</v>
@@ -41276,7 +41876,7 @@
         <v>46</v>
       </c>
       <c r="F1396">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G1396" t="s">
         <v>1575</v>
@@ -41299,7 +41899,7 @@
         <v>46</v>
       </c>
       <c r="F1397">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G1397" t="s">
         <v>1575</v>
@@ -41437,7 +42037,7 @@
         <v>46</v>
       </c>
       <c r="F1403">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G1403" t="s">
         <v>1575</v>
@@ -41506,7 +42106,7 @@
         <v>46</v>
       </c>
       <c r="F1406">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1406" t="s">
         <v>1575</v>
@@ -41736,7 +42336,7 @@
         <v>46</v>
       </c>
       <c r="F1416">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1416" t="s">
         <v>1575</v>
@@ -41805,7 +42405,7 @@
         <v>46</v>
       </c>
       <c r="F1419">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1419" t="s">
         <v>1575</v>
@@ -41845,13 +42445,13 @@
         <v>1184</v>
       </c>
       <c r="D1421">
-        <v>430</v>
+        <v>380</v>
       </c>
       <c r="E1421" t="s">
         <v>46</v>
       </c>
       <c r="F1421">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G1421" t="s">
         <v>1575</v>
@@ -42564,7 +43164,7 @@
         <v>46</v>
       </c>
       <c r="F1452">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1452" t="s">
         <v>1575</v>
@@ -43599,7 +44199,7 @@
         <v>46</v>
       </c>
       <c r="F1497">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1497" t="s">
         <v>1861</v>
@@ -44197,7 +44797,7 @@
         <v>46</v>
       </c>
       <c r="F1523">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1523" t="s">
         <v>1861</v>
@@ -44243,7 +44843,7 @@
         <v>46</v>
       </c>
       <c r="F1525">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1525" t="s">
         <v>1861</v>
@@ -44795,7 +45395,7 @@
         <v>46</v>
       </c>
       <c r="F1549">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1549" t="s">
         <v>1861</v>
@@ -44864,7 +45464,7 @@
         <v>46</v>
       </c>
       <c r="F1552">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1552" t="s">
         <v>1861</v>
@@ -44979,7 +45579,7 @@
         <v>46</v>
       </c>
       <c r="F1557">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1557" t="s">
         <v>1861</v>
@@ -45025,7 +45625,7 @@
         <v>46</v>
       </c>
       <c r="F1559">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1559" t="s">
         <v>1861</v>
@@ -46405,7 +47005,7 @@
         <v>46</v>
       </c>
       <c r="F1619">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1619" t="s">
         <v>2043</v>
@@ -47164,7 +47764,7 @@
         <v>46</v>
       </c>
       <c r="F1652">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1652" t="s">
         <v>2127</v>
@@ -48452,7 +49052,7 @@
         <v>46</v>
       </c>
       <c r="F1708">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1708" t="s">
         <v>2249</v>
@@ -48820,7 +49420,7 @@
         <v>46</v>
       </c>
       <c r="F1724">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1724" t="s">
         <v>2249</v>
@@ -50315,7 +50915,7 @@
         <v>46</v>
       </c>
       <c r="F1789">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G1789" t="s">
         <v>2417</v>
@@ -50430,7 +51030,7 @@
         <v>46</v>
       </c>
       <c r="F1794">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1794" t="s">
         <v>2435</v>
@@ -50660,7 +51260,7 @@
         <v>46</v>
       </c>
       <c r="F1804">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1804" t="s">
         <v>2443</v>
@@ -50683,7 +51283,7 @@
         <v>46</v>
       </c>
       <c r="F1805">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G1805" t="s">
         <v>2443</v>
@@ -50706,7 +51306,7 @@
         <v>46</v>
       </c>
       <c r="F1806">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1806" t="s">
         <v>2443</v>
@@ -51051,7 +51651,7 @@
         <v>46</v>
       </c>
       <c r="F1821">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1821" t="s">
         <v>2455</v>
@@ -51120,7 +51720,7 @@
         <v>46</v>
       </c>
       <c r="F1824">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1824" t="s">
         <v>2471</v>
@@ -51212,7 +51812,7 @@
         <v>46</v>
       </c>
       <c r="F1828">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G1828" t="s">
         <v>2471</v>
@@ -51281,7 +51881,7 @@
         <v>46</v>
       </c>
       <c r="F1831">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G1831" t="s">
         <v>2471</v>
@@ -51304,7 +51904,7 @@
         <v>46</v>
       </c>
       <c r="F1832">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G1832" t="s">
         <v>2471</v>
@@ -51626,7 +52226,7 @@
         <v>46</v>
       </c>
       <c r="F1846">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G1846" t="s">
         <v>2471</v>
@@ -51649,7 +52249,7 @@
         <v>46</v>
       </c>
       <c r="F1847">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G1847" t="s">
         <v>2471</v>
@@ -51695,7 +52295,7 @@
         <v>46</v>
       </c>
       <c r="F1849">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G1849" t="s">
         <v>2471</v>
@@ -52546,7 +53146,7 @@
         <v>46</v>
       </c>
       <c r="F1886">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G1886" t="s">
         <v>2543</v>
@@ -52753,7 +53353,7 @@
         <v>46</v>
       </c>
       <c r="F1895">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G1895" t="s">
         <v>2551</v>
@@ -53006,7 +53606,7 @@
         <v>46</v>
       </c>
       <c r="F1906">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G1906" t="s">
         <v>2551</v>
@@ -53029,7 +53629,7 @@
         <v>46</v>
       </c>
       <c r="F1907">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1907" t="s">
         <v>2551</v>
@@ -53719,7 +54319,7 @@
         <v>46</v>
       </c>
       <c r="F1937">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1937" t="s">
         <v>2584</v>
@@ -53834,7 +54434,7 @@
         <v>46</v>
       </c>
       <c r="F1942">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1942" t="s">
         <v>2590</v>
@@ -54409,7 +55009,7 @@
         <v>46</v>
       </c>
       <c r="F1967">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1967" t="s">
         <v>2612</v>
@@ -55559,7 +56159,7 @@
         <v>46</v>
       </c>
       <c r="F2017">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2017" t="s">
         <v>2678</v>
@@ -55743,7 +56343,7 @@
         <v>46</v>
       </c>
       <c r="F2025">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G2025" t="s">
         <v>2689</v>
@@ -55835,7 +56435,7 @@
         <v>46</v>
       </c>
       <c r="F2029">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G2029" t="s">
         <v>2689</v>
@@ -56042,7 +56642,7 @@
         <v>46</v>
       </c>
       <c r="F2038">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G2038" t="s">
         <v>2689</v>
@@ -56134,7 +56734,7 @@
         <v>46</v>
       </c>
       <c r="F2042">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G2042" t="s">
         <v>2717</v>
@@ -56249,7 +56849,7 @@
         <v>46</v>
       </c>
       <c r="F2047">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G2047" t="s">
         <v>2717</v>
@@ -56387,7 +56987,7 @@
         <v>46</v>
       </c>
       <c r="F2053">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G2053" t="s">
         <v>2717</v>
@@ -56433,7 +57033,7 @@
         <v>46</v>
       </c>
       <c r="F2055">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G2055" t="s">
         <v>2737</v>
@@ -56640,7 +57240,7 @@
         <v>46</v>
       </c>
       <c r="F2064">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G2064" t="s">
         <v>2737</v>
@@ -56939,7 +57539,7 @@
         <v>46</v>
       </c>
       <c r="F2077">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G2077" t="s">
         <v>2749</v>
@@ -56962,7 +57562,7 @@
         <v>46</v>
       </c>
       <c r="F2078">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G2078" t="s">
         <v>2749</v>
@@ -57054,7 +57654,7 @@
         <v>46</v>
       </c>
       <c r="F2082">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2082" t="s">
         <v>2749</v>
@@ -57399,7 +57999,7 @@
         <v>46</v>
       </c>
       <c r="F2097">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G2097" t="s">
         <v>2777</v>
@@ -57445,7 +58045,7 @@
         <v>46</v>
       </c>
       <c r="F2099">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G2099" t="s">
         <v>2777</v>
@@ -57468,7 +58068,7 @@
         <v>46</v>
       </c>
       <c r="F2100">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G2100" t="s">
         <v>2777</v>
@@ -57491,7 +58091,7 @@
         <v>46</v>
       </c>
       <c r="F2101">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G2101" t="s">
         <v>2777</v>
@@ -57514,7 +58114,7 @@
         <v>46</v>
       </c>
       <c r="F2102">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G2102" t="s">
         <v>2777</v>
@@ -57997,7 +58597,7 @@
         <v>46</v>
       </c>
       <c r="F2123">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2123" t="s">
         <v>2809</v>
@@ -58158,7 +58758,7 @@
         <v>46</v>
       </c>
       <c r="F2130">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G2130" t="s">
         <v>2822</v>
@@ -58411,7 +59011,7 @@
         <v>46</v>
       </c>
       <c r="F2141">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="G2141" t="s">
         <v>2840</v>
@@ -58503,7 +59103,7 @@
         <v>46</v>
       </c>
       <c r="F2145">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G2145" t="s">
         <v>2848</v>
@@ -58825,7 +59425,7 @@
         <v>46</v>
       </c>
       <c r="F2159">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G2159" t="s">
         <v>2848</v>
@@ -58940,7 +59540,7 @@
         <v>46</v>
       </c>
       <c r="F2164">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G2164" t="s">
         <v>2873</v>
@@ -59377,7 +59977,7 @@
         <v>46</v>
       </c>
       <c r="F2183">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G2183" t="s">
         <v>2886</v>
@@ -59469,7 +60069,7 @@
         <v>46</v>
       </c>
       <c r="F2187">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G2187" t="s">
         <v>2886</v>
@@ -59676,7 +60276,7 @@
         <v>46</v>
       </c>
       <c r="F2196">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G2196" t="s">
         <v>2909</v>
@@ -59722,7 +60322,7 @@
         <v>46</v>
       </c>
       <c r="F2198">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2198" t="s">
         <v>2909</v>
@@ -59929,7 +60529,7 @@
         <v>46</v>
       </c>
       <c r="F2207">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G2207" t="s">
         <v>2909</v>
@@ -59952,7 +60552,7 @@
         <v>46</v>
       </c>
       <c r="F2208">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G2208" t="s">
         <v>2909</v>
@@ -60113,7 +60713,7 @@
         <v>46</v>
       </c>
       <c r="F2215">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G2215" t="s">
         <v>2917</v>
@@ -60366,7 +60966,7 @@
         <v>46</v>
       </c>
       <c r="F2226">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G2226" t="s">
         <v>2928</v>
@@ -60416,6 +61016,3479 @@
       </c>
       <c r="G2228" t="s">
         <v>2928</v>
+      </c>
+    </row>
+    <row r="2229" spans="1:7">
+      <c r="A2229" t="s">
+        <v>2845</v>
+      </c>
+      <c r="B2229" t="s">
+        <v>2936</v>
+      </c>
+      <c r="C2229" t="s">
+        <v>2926</v>
+      </c>
+      <c r="D2229">
+        <v>600</v>
+      </c>
+      <c r="E2229" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2229">
+        <v>5</v>
+      </c>
+      <c r="G2229" t="s">
+        <v>2937</v>
+      </c>
+    </row>
+    <row r="2230" spans="1:7">
+      <c r="A2230" t="s">
+        <v>2845</v>
+      </c>
+      <c r="B2230" t="s">
+        <v>2938</v>
+      </c>
+      <c r="C2230" t="s">
+        <v>2939</v>
+      </c>
+      <c r="D2230">
+        <v>580</v>
+      </c>
+      <c r="E2230" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2230">
+        <v>1</v>
+      </c>
+      <c r="G2230" t="s">
+        <v>2937</v>
+      </c>
+    </row>
+    <row r="2231" spans="1:7">
+      <c r="A2231" t="s">
+        <v>2845</v>
+      </c>
+      <c r="B2231" t="s">
+        <v>2940</v>
+      </c>
+      <c r="C2231" t="s">
+        <v>2926</v>
+      </c>
+      <c r="D2231">
+        <v>600</v>
+      </c>
+      <c r="E2231" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2231">
+        <v>1</v>
+      </c>
+      <c r="G2231" t="s">
+        <v>2937</v>
+      </c>
+    </row>
+    <row r="2232" spans="1:7">
+      <c r="A2232" t="s">
+        <v>2845</v>
+      </c>
+      <c r="B2232" t="s">
+        <v>2941</v>
+      </c>
+      <c r="C2232" t="s">
+        <v>2856</v>
+      </c>
+      <c r="D2232">
+        <v>650</v>
+      </c>
+      <c r="E2232" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2232">
+        <v>3</v>
+      </c>
+      <c r="G2232" t="s">
+        <v>2937</v>
+      </c>
+    </row>
+    <row r="2233" spans="1:7">
+      <c r="A2233" t="s">
+        <v>2845</v>
+      </c>
+      <c r="B2233" t="s">
+        <v>2942</v>
+      </c>
+      <c r="C2233" t="s">
+        <v>2847</v>
+      </c>
+      <c r="D2233">
+        <v>550</v>
+      </c>
+      <c r="E2233" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2233">
+        <v>6</v>
+      </c>
+      <c r="G2233" t="s">
+        <v>2937</v>
+      </c>
+    </row>
+    <row r="2234" spans="1:7">
+      <c r="A2234" t="s">
+        <v>2845</v>
+      </c>
+      <c r="B2234" t="s">
+        <v>2943</v>
+      </c>
+      <c r="C2234" t="s">
+        <v>2847</v>
+      </c>
+      <c r="D2234">
+        <v>650</v>
+      </c>
+      <c r="E2234" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2234">
+        <v>8</v>
+      </c>
+      <c r="G2234" t="s">
+        <v>2937</v>
+      </c>
+    </row>
+    <row r="2235" spans="1:7">
+      <c r="A2235" t="s">
+        <v>2845</v>
+      </c>
+      <c r="B2235" t="s">
+        <v>2944</v>
+      </c>
+      <c r="C2235" t="s">
+        <v>2847</v>
+      </c>
+      <c r="D2235">
+        <v>650</v>
+      </c>
+      <c r="E2235" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2235">
+        <v>7</v>
+      </c>
+      <c r="G2235" t="s">
+        <v>2937</v>
+      </c>
+    </row>
+    <row r="2236" spans="1:7">
+      <c r="A2236" t="s">
+        <v>2845</v>
+      </c>
+      <c r="B2236" t="s">
+        <v>2945</v>
+      </c>
+      <c r="C2236" t="s">
+        <v>2847</v>
+      </c>
+      <c r="D2236">
+        <v>650</v>
+      </c>
+      <c r="E2236" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2236">
+        <v>2</v>
+      </c>
+      <c r="G2236" t="s">
+        <v>2946</v>
+      </c>
+    </row>
+    <row r="2237" spans="1:7">
+      <c r="A2237" t="s">
+        <v>2845</v>
+      </c>
+      <c r="B2237" t="s">
+        <v>2947</v>
+      </c>
+      <c r="C2237" t="s">
+        <v>2926</v>
+      </c>
+      <c r="D2237">
+        <v>600</v>
+      </c>
+      <c r="E2237" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2237">
+        <v>4</v>
+      </c>
+      <c r="G2237" t="s">
+        <v>2946</v>
+      </c>
+    </row>
+    <row r="2238" spans="1:7">
+      <c r="A2238" t="s">
+        <v>2845</v>
+      </c>
+      <c r="B2238" t="s">
+        <v>2948</v>
+      </c>
+      <c r="C2238" t="s">
+        <v>2847</v>
+      </c>
+      <c r="D2238">
+        <v>650</v>
+      </c>
+      <c r="E2238" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2238">
+        <v>7</v>
+      </c>
+      <c r="G2238" t="s">
+        <v>2946</v>
+      </c>
+    </row>
+    <row r="2239" spans="1:7">
+      <c r="A2239" t="s">
+        <v>2845</v>
+      </c>
+      <c r="B2239" t="s">
+        <v>2949</v>
+      </c>
+      <c r="C2239" t="s">
+        <v>2847</v>
+      </c>
+      <c r="D2239">
+        <v>550</v>
+      </c>
+      <c r="E2239" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2239">
+        <v>3</v>
+      </c>
+      <c r="G2239" t="s">
+        <v>2946</v>
+      </c>
+    </row>
+    <row r="2240" spans="1:7">
+      <c r="A2240" t="s">
+        <v>2845</v>
+      </c>
+      <c r="B2240" t="s">
+        <v>2950</v>
+      </c>
+      <c r="C2240" t="s">
+        <v>2847</v>
+      </c>
+      <c r="D2240">
+        <v>680</v>
+      </c>
+      <c r="E2240" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2240">
+        <v>3</v>
+      </c>
+      <c r="G2240" t="s">
+        <v>2946</v>
+      </c>
+    </row>
+    <row r="2241" spans="1:7">
+      <c r="A2241" t="s">
+        <v>2845</v>
+      </c>
+      <c r="B2241" t="s">
+        <v>2951</v>
+      </c>
+      <c r="C2241" t="s">
+        <v>2847</v>
+      </c>
+      <c r="D2241">
+        <v>680</v>
+      </c>
+      <c r="E2241" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2241">
+        <v>6</v>
+      </c>
+      <c r="G2241" t="s">
+        <v>2946</v>
+      </c>
+    </row>
+    <row r="2242" spans="1:7">
+      <c r="A2242" t="s">
+        <v>2845</v>
+      </c>
+      <c r="B2242" t="s">
+        <v>2952</v>
+      </c>
+      <c r="C2242" t="s">
+        <v>2847</v>
+      </c>
+      <c r="D2242">
+        <v>680</v>
+      </c>
+      <c r="E2242" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2242">
+        <v>10</v>
+      </c>
+      <c r="G2242" t="s">
+        <v>2946</v>
+      </c>
+    </row>
+    <row r="2243" spans="1:7">
+      <c r="A2243" t="s">
+        <v>2953</v>
+      </c>
+      <c r="B2243" t="s">
+        <v>2954</v>
+      </c>
+      <c r="C2243" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2243">
+        <v>10</v>
+      </c>
+      <c r="E2243" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2243">
+        <v>32</v>
+      </c>
+      <c r="G2243" t="s">
+        <v>2955</v>
+      </c>
+    </row>
+    <row r="2244" spans="1:7">
+      <c r="A2244" t="s">
+        <v>2845</v>
+      </c>
+      <c r="B2244" t="s">
+        <v>2956</v>
+      </c>
+      <c r="C2244" t="s">
+        <v>2847</v>
+      </c>
+      <c r="D2244">
+        <v>680</v>
+      </c>
+      <c r="E2244" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2244">
+        <v>4</v>
+      </c>
+      <c r="G2244" t="s">
+        <v>2957</v>
+      </c>
+    </row>
+    <row r="2245" spans="1:7">
+      <c r="A2245" t="s">
+        <v>2845</v>
+      </c>
+      <c r="B2245" t="s">
+        <v>2958</v>
+      </c>
+      <c r="C2245" t="s">
+        <v>2959</v>
+      </c>
+      <c r="D2245">
+        <v>690</v>
+      </c>
+      <c r="E2245" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2245">
+        <v>1</v>
+      </c>
+      <c r="G2245" t="s">
+        <v>2957</v>
+      </c>
+    </row>
+    <row r="2246" spans="1:7">
+      <c r="A2246" t="s">
+        <v>326</v>
+      </c>
+      <c r="B2246" t="s">
+        <v>2960</v>
+      </c>
+      <c r="C2246" t="s">
+        <v>285</v>
+      </c>
+      <c r="D2246">
+        <v>2250</v>
+      </c>
+      <c r="E2246" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2246">
+        <v>3</v>
+      </c>
+      <c r="G2246" t="s">
+        <v>2961</v>
+      </c>
+    </row>
+    <row r="2247" spans="1:7">
+      <c r="A2247" t="s">
+        <v>2962</v>
+      </c>
+      <c r="B2247" t="s">
+        <v>2963</v>
+      </c>
+      <c r="C2247" t="s">
+        <v>104</v>
+      </c>
+      <c r="D2247">
+        <v>350</v>
+      </c>
+      <c r="E2247" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2247">
+        <v>10</v>
+      </c>
+      <c r="G2247" t="s">
+        <v>2961</v>
+      </c>
+    </row>
+    <row r="2248" spans="1:7">
+      <c r="A2248" t="s">
+        <v>370</v>
+      </c>
+      <c r="B2248" t="s">
+        <v>2964</v>
+      </c>
+      <c r="C2248" t="s">
+        <v>83</v>
+      </c>
+      <c r="D2248">
+        <v>2400</v>
+      </c>
+      <c r="E2248" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2248">
+        <v>2</v>
+      </c>
+      <c r="G2248" t="s">
+        <v>2965</v>
+      </c>
+    </row>
+    <row r="2249" spans="1:7">
+      <c r="A2249" t="s">
+        <v>2966</v>
+      </c>
+      <c r="B2249" t="s">
+        <v>2967</v>
+      </c>
+      <c r="C2249" t="s">
+        <v>753</v>
+      </c>
+      <c r="D2249">
+        <v>1100</v>
+      </c>
+      <c r="E2249" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2249">
+        <v>6</v>
+      </c>
+      <c r="G2249" t="s">
+        <v>2968</v>
+      </c>
+    </row>
+    <row r="2250" spans="1:7">
+      <c r="A2250" t="s">
+        <v>2969</v>
+      </c>
+      <c r="B2250" t="s">
+        <v>2970</v>
+      </c>
+      <c r="C2250" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2250">
+        <v>1600</v>
+      </c>
+      <c r="E2250" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2250">
+        <v>1</v>
+      </c>
+      <c r="G2250" t="s">
+        <v>2971</v>
+      </c>
+    </row>
+    <row r="2251" spans="1:7">
+      <c r="A2251" t="s">
+        <v>2972</v>
+      </c>
+      <c r="B2251" t="s">
+        <v>2973</v>
+      </c>
+      <c r="C2251" t="s">
+        <v>2974</v>
+      </c>
+      <c r="D2251">
+        <v>490</v>
+      </c>
+      <c r="E2251" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2251">
+        <v>4</v>
+      </c>
+      <c r="G2251" t="s">
+        <v>2975</v>
+      </c>
+    </row>
+    <row r="2252" spans="1:7">
+      <c r="A2252" t="s">
+        <v>2976</v>
+      </c>
+      <c r="B2252" t="s">
+        <v>2977</v>
+      </c>
+      <c r="C2252" t="s">
+        <v>2978</v>
+      </c>
+      <c r="D2252">
+        <v>70</v>
+      </c>
+      <c r="E2252" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2252">
+        <v>8</v>
+      </c>
+      <c r="G2252" t="s">
+        <v>2975</v>
+      </c>
+    </row>
+    <row r="2253" spans="1:7">
+      <c r="A2253" t="s">
+        <v>2979</v>
+      </c>
+      <c r="B2253" t="s">
+        <v>2980</v>
+      </c>
+      <c r="C2253" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2253">
+        <v>1800</v>
+      </c>
+      <c r="E2253" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2253">
+        <v>4</v>
+      </c>
+      <c r="G2253" t="s">
+        <v>2975</v>
+      </c>
+    </row>
+    <row r="2254" spans="1:7">
+      <c r="A2254" t="s">
+        <v>2981</v>
+      </c>
+      <c r="B2254" t="s">
+        <v>2982</v>
+      </c>
+      <c r="C2254" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2254">
+        <v>120</v>
+      </c>
+      <c r="E2254" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2254">
+        <v>6</v>
+      </c>
+      <c r="G2254" t="s">
+        <v>2975</v>
+      </c>
+    </row>
+    <row r="2255" spans="1:7">
+      <c r="A2255" t="s">
+        <v>2983</v>
+      </c>
+      <c r="B2255" t="s">
+        <v>2984</v>
+      </c>
+      <c r="C2255" t="s">
+        <v>2985</v>
+      </c>
+      <c r="D2255">
+        <v>4500</v>
+      </c>
+      <c r="E2255" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2255">
+        <v>1</v>
+      </c>
+      <c r="G2255" t="s">
+        <v>2986</v>
+      </c>
+    </row>
+    <row r="2256" spans="1:7">
+      <c r="A2256" t="s">
+        <v>2987</v>
+      </c>
+      <c r="B2256" t="s">
+        <v>2988</v>
+      </c>
+      <c r="C2256" t="s">
+        <v>2985</v>
+      </c>
+      <c r="D2256">
+        <v>750</v>
+      </c>
+      <c r="E2256" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2256">
+        <v>4</v>
+      </c>
+      <c r="G2256" t="s">
+        <v>2986</v>
+      </c>
+    </row>
+    <row r="2257" spans="1:7">
+      <c r="A2257" t="s">
+        <v>631</v>
+      </c>
+      <c r="B2257" t="s">
+        <v>2989</v>
+      </c>
+      <c r="C2257" t="s">
+        <v>2990</v>
+      </c>
+      <c r="D2257">
+        <v>1450</v>
+      </c>
+      <c r="E2257" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2257">
+        <v>8</v>
+      </c>
+      <c r="G2257" t="s">
+        <v>2991</v>
+      </c>
+    </row>
+    <row r="2258" spans="1:7">
+      <c r="A2258" t="s">
+        <v>2992</v>
+      </c>
+      <c r="B2258" t="s">
+        <v>2993</v>
+      </c>
+      <c r="C2258" t="s">
+        <v>2994</v>
+      </c>
+      <c r="D2258">
+        <v>550</v>
+      </c>
+      <c r="E2258" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2258">
+        <v>5</v>
+      </c>
+      <c r="G2258" t="s">
+        <v>2995</v>
+      </c>
+    </row>
+    <row r="2259" spans="1:7">
+      <c r="A2259" t="s">
+        <v>2996</v>
+      </c>
+      <c r="B2259" t="s">
+        <v>2997</v>
+      </c>
+      <c r="C2259" t="s">
+        <v>2998</v>
+      </c>
+      <c r="D2259">
+        <v>90</v>
+      </c>
+      <c r="E2259" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2259">
+        <v>7</v>
+      </c>
+      <c r="G2259" t="s">
+        <v>2995</v>
+      </c>
+    </row>
+    <row r="2260" spans="1:7">
+      <c r="A2260" t="s">
+        <v>2999</v>
+      </c>
+      <c r="B2260" t="s">
+        <v>3000</v>
+      </c>
+      <c r="C2260" t="s">
+        <v>3001</v>
+      </c>
+      <c r="D2260">
+        <v>10500</v>
+      </c>
+      <c r="E2260" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2260">
+        <v>2</v>
+      </c>
+      <c r="G2260" t="s">
+        <v>3002</v>
+      </c>
+    </row>
+    <row r="2261" spans="1:7">
+      <c r="A2261" t="s">
+        <v>3003</v>
+      </c>
+      <c r="B2261" t="s">
+        <v>3004</v>
+      </c>
+      <c r="C2261" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2261">
+        <v>780</v>
+      </c>
+      <c r="E2261" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2261">
+        <v>1</v>
+      </c>
+      <c r="G2261" t="s">
+        <v>3002</v>
+      </c>
+    </row>
+    <row r="2262" spans="1:7">
+      <c r="A2262" t="s">
+        <v>2449</v>
+      </c>
+      <c r="B2262" t="s">
+        <v>3005</v>
+      </c>
+      <c r="C2262" t="s">
+        <v>98</v>
+      </c>
+      <c r="D2262">
+        <v>2700</v>
+      </c>
+      <c r="E2262" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2262">
+        <v>1</v>
+      </c>
+      <c r="G2262" t="s">
+        <v>3006</v>
+      </c>
+    </row>
+    <row r="2263" spans="1:7">
+      <c r="A2263" t="s">
+        <v>497</v>
+      </c>
+      <c r="B2263" t="s">
+        <v>3007</v>
+      </c>
+      <c r="C2263" t="s">
+        <v>83</v>
+      </c>
+      <c r="D2263">
+        <v>950</v>
+      </c>
+      <c r="E2263" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2263">
+        <v>5</v>
+      </c>
+      <c r="G2263" t="s">
+        <v>3006</v>
+      </c>
+    </row>
+    <row r="2264" spans="1:7">
+      <c r="A2264" t="s">
+        <v>3008</v>
+      </c>
+      <c r="B2264">
+        <v>703205778100</v>
+      </c>
+      <c r="C2264" t="s">
+        <v>3009</v>
+      </c>
+      <c r="D2264">
+        <v>890</v>
+      </c>
+      <c r="E2264" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2264">
+        <v>10</v>
+      </c>
+      <c r="G2264" t="s">
+        <v>3010</v>
+      </c>
+    </row>
+    <row r="2265" spans="1:7">
+      <c r="A2265" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B2265">
+        <v>8697640012504</v>
+      </c>
+      <c r="C2265" t="s">
+        <v>3009</v>
+      </c>
+      <c r="D2265">
+        <v>920</v>
+      </c>
+      <c r="E2265" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2265">
+        <v>10</v>
+      </c>
+      <c r="G2265" t="s">
+        <v>3010</v>
+      </c>
+    </row>
+    <row r="2266" spans="1:7">
+      <c r="A2266" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B2266">
+        <v>8697640006527</v>
+      </c>
+      <c r="C2266" t="s">
+        <v>3009</v>
+      </c>
+      <c r="D2266">
+        <v>1200</v>
+      </c>
+      <c r="E2266" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2266">
+        <v>10</v>
+      </c>
+      <c r="G2266" t="s">
+        <v>3010</v>
+      </c>
+    </row>
+    <row r="2267" spans="1:7">
+      <c r="A2267" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B2267">
+        <v>8697640003762</v>
+      </c>
+      <c r="C2267" t="s">
+        <v>3009</v>
+      </c>
+      <c r="D2267">
+        <v>1200</v>
+      </c>
+      <c r="E2267" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2267">
+        <v>20</v>
+      </c>
+      <c r="G2267" t="s">
+        <v>3010</v>
+      </c>
+    </row>
+    <row r="2268" spans="1:7">
+      <c r="A2268" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B2268">
+        <v>8697640084143</v>
+      </c>
+      <c r="C2268" t="s">
+        <v>3009</v>
+      </c>
+      <c r="D2268">
+        <v>1420</v>
+      </c>
+      <c r="E2268" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2268">
+        <v>36</v>
+      </c>
+      <c r="G2268" t="s">
+        <v>3011</v>
+      </c>
+    </row>
+    <row r="2269" spans="1:7">
+      <c r="A2269" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B2269">
+        <v>8697640011033</v>
+      </c>
+      <c r="C2269" t="s">
+        <v>3009</v>
+      </c>
+      <c r="D2269">
+        <v>1300</v>
+      </c>
+      <c r="E2269" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2269">
+        <v>18</v>
+      </c>
+      <c r="G2269" t="s">
+        <v>3011</v>
+      </c>
+    </row>
+    <row r="2270" spans="1:7">
+      <c r="A2270" t="s">
+        <v>3012</v>
+      </c>
+      <c r="B2270">
+        <v>8697640025832</v>
+      </c>
+      <c r="C2270" t="s">
+        <v>3009</v>
+      </c>
+      <c r="D2270">
+        <v>900</v>
+      </c>
+      <c r="E2270" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2270">
+        <v>6</v>
+      </c>
+      <c r="G2270" t="s">
+        <v>3011</v>
+      </c>
+    </row>
+    <row r="2271" spans="1:7">
+      <c r="A2271" t="s">
+        <v>3013</v>
+      </c>
+      <c r="B2271">
+        <v>4013790996053</v>
+      </c>
+      <c r="C2271" t="s">
+        <v>266</v>
+      </c>
+      <c r="D2271">
+        <v>75</v>
+      </c>
+      <c r="E2271" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2271">
+        <v>30</v>
+      </c>
+      <c r="G2271" t="s">
+        <v>3014</v>
+      </c>
+    </row>
+    <row r="2272" spans="1:7">
+      <c r="A2272" t="s">
+        <v>3015</v>
+      </c>
+      <c r="B2272">
+        <v>4013790341150</v>
+      </c>
+      <c r="C2272" t="s">
+        <v>266</v>
+      </c>
+      <c r="D2272">
+        <v>330</v>
+      </c>
+      <c r="E2272" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2272">
+        <v>30</v>
+      </c>
+      <c r="G2272" t="s">
+        <v>3014</v>
+      </c>
+    </row>
+    <row r="2273" spans="1:7">
+      <c r="A2273" t="s">
+        <v>731</v>
+      </c>
+      <c r="B2273">
+        <v>4582702620800</v>
+      </c>
+      <c r="C2273" t="s">
+        <v>712</v>
+      </c>
+      <c r="D2273">
+        <v>650</v>
+      </c>
+      <c r="E2273" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2273">
+        <v>10</v>
+      </c>
+      <c r="G2273" t="s">
+        <v>3014</v>
+      </c>
+    </row>
+    <row r="2274" spans="1:7">
+      <c r="A2274" t="s">
+        <v>3016</v>
+      </c>
+      <c r="B2274">
+        <v>3456218045907</v>
+      </c>
+      <c r="C2274" t="s">
+        <v>3017</v>
+      </c>
+      <c r="D2274">
+        <v>60</v>
+      </c>
+      <c r="E2274" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2274">
+        <v>60</v>
+      </c>
+      <c r="G2274" t="s">
+        <v>3014</v>
+      </c>
+    </row>
+    <row r="2275" spans="1:7">
+      <c r="A2275" t="s">
+        <v>3018</v>
+      </c>
+      <c r="B2275">
+        <v>3456218044787</v>
+      </c>
+      <c r="C2275" t="s">
+        <v>3017</v>
+      </c>
+      <c r="D2275">
+        <v>45</v>
+      </c>
+      <c r="E2275" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2275">
+        <v>40</v>
+      </c>
+      <c r="G2275" t="s">
+        <v>3014</v>
+      </c>
+    </row>
+    <row r="2276" spans="1:7">
+      <c r="A2276" t="s">
+        <v>3018</v>
+      </c>
+      <c r="B2276">
+        <v>3456218046991</v>
+      </c>
+      <c r="C2276" t="s">
+        <v>3017</v>
+      </c>
+      <c r="D2276">
+        <v>45</v>
+      </c>
+      <c r="E2276" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2276">
+        <v>40</v>
+      </c>
+      <c r="G2276" t="s">
+        <v>3014</v>
+      </c>
+    </row>
+    <row r="2277" spans="1:7">
+      <c r="A2277" t="s">
+        <v>3019</v>
+      </c>
+      <c r="B2277" t="s">
+        <v>3020</v>
+      </c>
+      <c r="C2277" t="s">
+        <v>98</v>
+      </c>
+      <c r="D2277">
+        <v>950</v>
+      </c>
+      <c r="E2277" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2277">
+        <v>4</v>
+      </c>
+      <c r="G2277" t="s">
+        <v>3021</v>
+      </c>
+    </row>
+    <row r="2278" spans="1:7">
+      <c r="A2278" t="s">
+        <v>3022</v>
+      </c>
+      <c r="B2278" t="s">
+        <v>3023</v>
+      </c>
+      <c r="C2278" t="s">
+        <v>3024</v>
+      </c>
+      <c r="D2278">
+        <v>700</v>
+      </c>
+      <c r="E2278" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2278">
+        <v>2</v>
+      </c>
+      <c r="G2278" t="s">
+        <v>3021</v>
+      </c>
+    </row>
+    <row r="2279" spans="1:7">
+      <c r="A2279" t="s">
+        <v>2406</v>
+      </c>
+      <c r="B2279">
+        <v>50060</v>
+      </c>
+      <c r="C2279" t="s">
+        <v>1566</v>
+      </c>
+      <c r="D2279">
+        <v>1350</v>
+      </c>
+      <c r="E2279" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2279">
+        <v>10</v>
+      </c>
+      <c r="G2279" t="s">
+        <v>3025</v>
+      </c>
+    </row>
+    <row r="2280" spans="1:7">
+      <c r="A2280" t="s">
+        <v>869</v>
+      </c>
+      <c r="B2280" t="s">
+        <v>3026</v>
+      </c>
+      <c r="C2280" t="s">
+        <v>767</v>
+      </c>
+      <c r="D2280">
+        <v>450</v>
+      </c>
+      <c r="E2280" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2280">
+        <v>10</v>
+      </c>
+      <c r="G2280" t="s">
+        <v>3025</v>
+      </c>
+    </row>
+    <row r="2281" spans="1:7">
+      <c r="A2281" t="s">
+        <v>3027</v>
+      </c>
+      <c r="B2281">
+        <v>5456156156</v>
+      </c>
+      <c r="C2281" t="s">
+        <v>760</v>
+      </c>
+      <c r="D2281">
+        <v>2450</v>
+      </c>
+      <c r="E2281" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2281">
+        <v>2</v>
+      </c>
+      <c r="G2281" t="s">
+        <v>3028</v>
+      </c>
+    </row>
+    <row r="2282" spans="1:7">
+      <c r="A2282" t="s">
+        <v>3029</v>
+      </c>
+      <c r="B2282" t="s">
+        <v>3030</v>
+      </c>
+      <c r="C2282" t="s">
+        <v>285</v>
+      </c>
+      <c r="D2282">
+        <v>9500</v>
+      </c>
+      <c r="E2282" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2282">
+        <v>1</v>
+      </c>
+      <c r="G2282" t="s">
+        <v>3031</v>
+      </c>
+    </row>
+    <row r="2283" spans="1:7">
+      <c r="A2283" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2283" t="s">
+        <v>3033</v>
+      </c>
+      <c r="C2283" t="s">
+        <v>2847</v>
+      </c>
+      <c r="D2283">
+        <v>90</v>
+      </c>
+      <c r="E2283" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2283">
+        <v>1</v>
+      </c>
+      <c r="G2283" t="s">
+        <v>3034</v>
+      </c>
+    </row>
+    <row r="2284" spans="1:7">
+      <c r="A2284" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2284" t="s">
+        <v>3035</v>
+      </c>
+      <c r="C2284" t="s">
+        <v>2939</v>
+      </c>
+      <c r="D2284">
+        <v>100</v>
+      </c>
+      <c r="E2284" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2284">
+        <v>4</v>
+      </c>
+      <c r="G2284" t="s">
+        <v>3034</v>
+      </c>
+    </row>
+    <row r="2285" spans="1:7">
+      <c r="A2285" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2285" t="s">
+        <v>3036</v>
+      </c>
+      <c r="C2285" t="s">
+        <v>3037</v>
+      </c>
+      <c r="D2285">
+        <v>150</v>
+      </c>
+      <c r="E2285" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2285">
+        <v>0</v>
+      </c>
+      <c r="G2285" t="s">
+        <v>3034</v>
+      </c>
+    </row>
+    <row r="2286" spans="1:7">
+      <c r="A2286" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2286" t="s">
+        <v>3038</v>
+      </c>
+      <c r="C2286" t="s">
+        <v>130</v>
+      </c>
+      <c r="D2286">
+        <v>300</v>
+      </c>
+      <c r="E2286" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2286">
+        <v>2</v>
+      </c>
+      <c r="G2286" t="s">
+        <v>3034</v>
+      </c>
+    </row>
+    <row r="2287" spans="1:7">
+      <c r="A2287" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2287" t="s">
+        <v>3039</v>
+      </c>
+      <c r="C2287" t="s">
+        <v>104</v>
+      </c>
+      <c r="D2287">
+        <v>95</v>
+      </c>
+      <c r="E2287" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2287">
+        <v>2</v>
+      </c>
+      <c r="G2287" t="s">
+        <v>3034</v>
+      </c>
+    </row>
+    <row r="2288" spans="1:7">
+      <c r="A2288" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2288" t="s">
+        <v>3040</v>
+      </c>
+      <c r="C2288" t="s">
+        <v>2847</v>
+      </c>
+      <c r="D2288">
+        <v>100</v>
+      </c>
+      <c r="E2288" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2288">
+        <v>3</v>
+      </c>
+      <c r="G2288" t="s">
+        <v>3034</v>
+      </c>
+    </row>
+    <row r="2289" spans="1:7">
+      <c r="A2289" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2289" t="s">
+        <v>3041</v>
+      </c>
+      <c r="C2289" t="s">
+        <v>335</v>
+      </c>
+      <c r="D2289">
+        <v>140</v>
+      </c>
+      <c r="E2289" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2289">
+        <v>2</v>
+      </c>
+      <c r="G2289" t="s">
+        <v>3034</v>
+      </c>
+    </row>
+    <row r="2290" spans="1:7">
+      <c r="A2290" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2290" t="s">
+        <v>3042</v>
+      </c>
+      <c r="C2290" t="s">
+        <v>104</v>
+      </c>
+      <c r="D2290">
+        <v>225</v>
+      </c>
+      <c r="E2290" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2290">
+        <v>4</v>
+      </c>
+      <c r="G2290" t="s">
+        <v>3034</v>
+      </c>
+    </row>
+    <row r="2291" spans="1:7">
+      <c r="A2291" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2291" t="s">
+        <v>3043</v>
+      </c>
+      <c r="C2291" t="s">
+        <v>2939</v>
+      </c>
+      <c r="D2291">
+        <v>80</v>
+      </c>
+      <c r="E2291" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2291">
+        <v>2</v>
+      </c>
+      <c r="G2291" t="s">
+        <v>3034</v>
+      </c>
+    </row>
+    <row r="2292" spans="1:7">
+      <c r="A2292" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2292" t="s">
+        <v>3044</v>
+      </c>
+      <c r="C2292" t="s">
+        <v>104</v>
+      </c>
+      <c r="D2292">
+        <v>90</v>
+      </c>
+      <c r="E2292" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2292">
+        <v>1</v>
+      </c>
+      <c r="G2292" t="s">
+        <v>3034</v>
+      </c>
+    </row>
+    <row r="2293" spans="1:7">
+      <c r="A2293" t="s">
+        <v>2449</v>
+      </c>
+      <c r="B2293" t="s">
+        <v>3045</v>
+      </c>
+      <c r="C2293" t="s">
+        <v>760</v>
+      </c>
+      <c r="D2293">
+        <v>2200</v>
+      </c>
+      <c r="E2293" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2293">
+        <v>2</v>
+      </c>
+      <c r="G2293" t="s">
+        <v>3046</v>
+      </c>
+    </row>
+    <row r="2294" spans="1:7">
+      <c r="A2294" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2294" t="s">
+        <v>3047</v>
+      </c>
+      <c r="C2294" t="s">
+        <v>753</v>
+      </c>
+      <c r="D2294">
+        <v>1300</v>
+      </c>
+      <c r="E2294" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2294">
+        <v>2</v>
+      </c>
+      <c r="G2294" t="s">
+        <v>3046</v>
+      </c>
+    </row>
+    <row r="2295" spans="1:7">
+      <c r="A2295" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2295" t="s">
+        <v>3048</v>
+      </c>
+      <c r="C2295" t="s">
+        <v>760</v>
+      </c>
+      <c r="D2295">
+        <v>1300</v>
+      </c>
+      <c r="E2295" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2295">
+        <v>5</v>
+      </c>
+      <c r="G2295" t="s">
+        <v>3046</v>
+      </c>
+    </row>
+    <row r="2296" spans="1:7">
+      <c r="A2296" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2296" t="s">
+        <v>3049</v>
+      </c>
+      <c r="C2296" t="s">
+        <v>2847</v>
+      </c>
+      <c r="D2296">
+        <v>90</v>
+      </c>
+      <c r="E2296" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2296">
+        <v>8</v>
+      </c>
+      <c r="G2296" t="s">
+        <v>3050</v>
+      </c>
+    </row>
+    <row r="2297" spans="1:7">
+      <c r="A2297" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2297" t="s">
+        <v>3051</v>
+      </c>
+      <c r="C2297" t="s">
+        <v>2847</v>
+      </c>
+      <c r="D2297">
+        <v>90</v>
+      </c>
+      <c r="E2297" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2297">
+        <v>5</v>
+      </c>
+      <c r="G2297" t="s">
+        <v>3050</v>
+      </c>
+    </row>
+    <row r="2298" spans="1:7">
+      <c r="A2298" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2298" t="s">
+        <v>3052</v>
+      </c>
+      <c r="C2298" t="s">
+        <v>3053</v>
+      </c>
+      <c r="D2298">
+        <v>80</v>
+      </c>
+      <c r="E2298" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2298">
+        <v>19</v>
+      </c>
+      <c r="G2298" t="s">
+        <v>3050</v>
+      </c>
+    </row>
+    <row r="2299" spans="1:7">
+      <c r="A2299" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2299" t="s">
+        <v>3054</v>
+      </c>
+      <c r="C2299" t="s">
+        <v>3055</v>
+      </c>
+      <c r="D2299">
+        <v>240</v>
+      </c>
+      <c r="E2299" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2299">
+        <v>3</v>
+      </c>
+      <c r="G2299" t="s">
+        <v>3050</v>
+      </c>
+    </row>
+    <row r="2300" spans="1:7">
+      <c r="A2300" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2300" t="s">
+        <v>3056</v>
+      </c>
+      <c r="C2300" t="s">
+        <v>3037</v>
+      </c>
+      <c r="D2300">
+        <v>260</v>
+      </c>
+      <c r="E2300" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2300">
+        <v>2</v>
+      </c>
+      <c r="G2300" t="s">
+        <v>3050</v>
+      </c>
+    </row>
+    <row r="2301" spans="1:7">
+      <c r="A2301" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2301" t="s">
+        <v>3057</v>
+      </c>
+      <c r="C2301" t="s">
+        <v>2847</v>
+      </c>
+      <c r="D2301">
+        <v>170</v>
+      </c>
+      <c r="E2301" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2301">
+        <v>10</v>
+      </c>
+      <c r="G2301" t="s">
+        <v>3050</v>
+      </c>
+    </row>
+    <row r="2302" spans="1:7">
+      <c r="A2302" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2302" t="s">
+        <v>3058</v>
+      </c>
+      <c r="C2302" t="s">
+        <v>2847</v>
+      </c>
+      <c r="D2302">
+        <v>160</v>
+      </c>
+      <c r="E2302" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2302">
+        <v>8</v>
+      </c>
+      <c r="G2302" t="s">
+        <v>3050</v>
+      </c>
+    </row>
+    <row r="2303" spans="1:7">
+      <c r="A2303" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2303" t="s">
+        <v>3059</v>
+      </c>
+      <c r="C2303" t="s">
+        <v>3060</v>
+      </c>
+      <c r="D2303">
+        <v>90</v>
+      </c>
+      <c r="E2303" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2303">
+        <v>1</v>
+      </c>
+      <c r="G2303" t="s">
+        <v>3050</v>
+      </c>
+    </row>
+    <row r="2304" spans="1:7">
+      <c r="A2304" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2304" t="s">
+        <v>3061</v>
+      </c>
+      <c r="C2304" t="s">
+        <v>3062</v>
+      </c>
+      <c r="D2304">
+        <v>120</v>
+      </c>
+      <c r="E2304" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2304">
+        <v>1</v>
+      </c>
+      <c r="G2304" t="s">
+        <v>3063</v>
+      </c>
+    </row>
+    <row r="2305" spans="1:7">
+      <c r="A2305" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2305" t="s">
+        <v>3064</v>
+      </c>
+      <c r="C2305" t="s">
+        <v>108</v>
+      </c>
+      <c r="D2305">
+        <v>70</v>
+      </c>
+      <c r="E2305" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2305">
+        <v>4</v>
+      </c>
+      <c r="G2305" t="s">
+        <v>3063</v>
+      </c>
+    </row>
+    <row r="2306" spans="1:7">
+      <c r="A2306" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2306" t="s">
+        <v>3065</v>
+      </c>
+      <c r="C2306" t="s">
+        <v>3066</v>
+      </c>
+      <c r="D2306">
+        <v>180</v>
+      </c>
+      <c r="E2306" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2306">
+        <v>5</v>
+      </c>
+      <c r="G2306" t="s">
+        <v>3063</v>
+      </c>
+    </row>
+    <row r="2307" spans="1:7">
+      <c r="A2307" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2307" t="s">
+        <v>3067</v>
+      </c>
+      <c r="C2307" t="s">
+        <v>3068</v>
+      </c>
+      <c r="D2307">
+        <v>400</v>
+      </c>
+      <c r="E2307" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2307">
+        <v>1</v>
+      </c>
+      <c r="G2307" t="s">
+        <v>3063</v>
+      </c>
+    </row>
+    <row r="2308" spans="1:7">
+      <c r="A2308" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2308" t="s">
+        <v>3069</v>
+      </c>
+      <c r="C2308" t="s">
+        <v>3066</v>
+      </c>
+      <c r="D2308">
+        <v>300</v>
+      </c>
+      <c r="E2308" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2308">
+        <v>4</v>
+      </c>
+      <c r="G2308" t="s">
+        <v>3063</v>
+      </c>
+    </row>
+    <row r="2309" spans="1:7">
+      <c r="A2309" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2309" t="s">
+        <v>3070</v>
+      </c>
+      <c r="C2309" t="s">
+        <v>3071</v>
+      </c>
+      <c r="D2309">
+        <v>450</v>
+      </c>
+      <c r="E2309" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2309">
+        <v>8</v>
+      </c>
+      <c r="G2309" t="s">
+        <v>3063</v>
+      </c>
+    </row>
+    <row r="2310" spans="1:7">
+      <c r="A2310" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2310" t="s">
+        <v>3072</v>
+      </c>
+      <c r="C2310" t="s">
+        <v>3055</v>
+      </c>
+      <c r="D2310">
+        <v>80</v>
+      </c>
+      <c r="E2310" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2310">
+        <v>1</v>
+      </c>
+      <c r="G2310" t="s">
+        <v>3073</v>
+      </c>
+    </row>
+    <row r="2311" spans="1:7">
+      <c r="A2311" t="s">
+        <v>73</v>
+      </c>
+      <c r="B2311" t="s">
+        <v>3074</v>
+      </c>
+      <c r="C2311" t="s">
+        <v>71</v>
+      </c>
+      <c r="D2311">
+        <v>1650</v>
+      </c>
+      <c r="E2311" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2311">
+        <v>2</v>
+      </c>
+      <c r="G2311" t="s">
+        <v>3075</v>
+      </c>
+    </row>
+    <row r="2312" spans="1:7">
+      <c r="A2312" t="s">
+        <v>73</v>
+      </c>
+      <c r="B2312" t="s">
+        <v>3076</v>
+      </c>
+      <c r="C2312" t="s">
+        <v>71</v>
+      </c>
+      <c r="D2312">
+        <v>1650</v>
+      </c>
+      <c r="E2312" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2312">
+        <v>2</v>
+      </c>
+      <c r="G2312" t="s">
+        <v>3075</v>
+      </c>
+    </row>
+    <row r="2313" spans="1:7">
+      <c r="A2313" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2313">
+        <v>7316571817347</v>
+      </c>
+      <c r="C2313" t="s">
+        <v>153</v>
+      </c>
+      <c r="D2313">
+        <v>200</v>
+      </c>
+      <c r="E2313" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2313">
+        <v>6</v>
+      </c>
+      <c r="G2313" t="s">
+        <v>3075</v>
+      </c>
+    </row>
+    <row r="2314" spans="1:7">
+      <c r="A2314" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2314">
+        <v>4549250141300</v>
+      </c>
+      <c r="C2314" t="s">
+        <v>3037</v>
+      </c>
+      <c r="D2314">
+        <v>200</v>
+      </c>
+      <c r="E2314" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2314">
+        <v>11</v>
+      </c>
+      <c r="G2314" t="s">
+        <v>3075</v>
+      </c>
+    </row>
+    <row r="2315" spans="1:7">
+      <c r="A2315" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2315">
+        <v>4549250412547</v>
+      </c>
+      <c r="C2315" t="s">
+        <v>3037</v>
+      </c>
+      <c r="D2315">
+        <v>120</v>
+      </c>
+      <c r="E2315" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2315">
+        <v>1</v>
+      </c>
+      <c r="G2315" t="s">
+        <v>3075</v>
+      </c>
+    </row>
+    <row r="2316" spans="1:7">
+      <c r="A2316" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2316" t="s">
+        <v>3077</v>
+      </c>
+      <c r="C2316" t="s">
+        <v>3037</v>
+      </c>
+      <c r="D2316">
+        <v>160</v>
+      </c>
+      <c r="E2316" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2316">
+        <v>10</v>
+      </c>
+      <c r="G2316" t="s">
+        <v>3078</v>
+      </c>
+    </row>
+    <row r="2317" spans="1:7">
+      <c r="A2317" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2317">
+        <v>4549250140150</v>
+      </c>
+      <c r="C2317" t="s">
+        <v>3037</v>
+      </c>
+      <c r="D2317">
+        <v>180</v>
+      </c>
+      <c r="E2317" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2317">
+        <v>10</v>
+      </c>
+      <c r="G2317" t="s">
+        <v>3078</v>
+      </c>
+    </row>
+    <row r="2318" spans="1:7">
+      <c r="A2318" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2318">
+        <v>4549250140716</v>
+      </c>
+      <c r="C2318" t="s">
+        <v>3037</v>
+      </c>
+      <c r="D2318">
+        <v>180</v>
+      </c>
+      <c r="E2318" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2318">
+        <v>10</v>
+      </c>
+      <c r="G2318" t="s">
+        <v>3078</v>
+      </c>
+    </row>
+    <row r="2319" spans="1:7">
+      <c r="A2319" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2319" t="s">
+        <v>3079</v>
+      </c>
+      <c r="C2319" t="s">
+        <v>3055</v>
+      </c>
+      <c r="D2319">
+        <v>120</v>
+      </c>
+      <c r="E2319" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2319">
+        <v>1</v>
+      </c>
+      <c r="G2319" t="s">
+        <v>3078</v>
+      </c>
+    </row>
+    <row r="2320" spans="1:7">
+      <c r="A2320" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2320" t="s">
+        <v>3080</v>
+      </c>
+      <c r="C2320" t="s">
+        <v>2939</v>
+      </c>
+      <c r="D2320">
+        <v>200</v>
+      </c>
+      <c r="E2320" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2320">
+        <v>2</v>
+      </c>
+      <c r="G2320" t="s">
+        <v>3078</v>
+      </c>
+    </row>
+    <row r="2321" spans="1:7">
+      <c r="A2321" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2321" t="s">
+        <v>3081</v>
+      </c>
+      <c r="C2321" t="s">
+        <v>3055</v>
+      </c>
+      <c r="D2321">
+        <v>450</v>
+      </c>
+      <c r="E2321" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2321">
+        <v>3</v>
+      </c>
+      <c r="G2321" t="s">
+        <v>3078</v>
+      </c>
+    </row>
+    <row r="2322" spans="1:7">
+      <c r="A2322" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2322" t="s">
+        <v>3082</v>
+      </c>
+      <c r="C2322" t="s">
+        <v>3053</v>
+      </c>
+      <c r="D2322">
+        <v>160</v>
+      </c>
+      <c r="E2322" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2322">
+        <v>4</v>
+      </c>
+      <c r="G2322" t="s">
+        <v>3078</v>
+      </c>
+    </row>
+    <row r="2323" spans="1:7">
+      <c r="A2323" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2323" t="s">
+        <v>3083</v>
+      </c>
+      <c r="C2323" t="s">
+        <v>3055</v>
+      </c>
+      <c r="D2323">
+        <v>450</v>
+      </c>
+      <c r="E2323" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2323">
+        <v>5</v>
+      </c>
+      <c r="G2323" t="s">
+        <v>3078</v>
+      </c>
+    </row>
+    <row r="2324" spans="1:7">
+      <c r="A2324" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2324">
+        <v>3517022600</v>
+      </c>
+      <c r="C2324" t="s">
+        <v>753</v>
+      </c>
+      <c r="D2324">
+        <v>1350</v>
+      </c>
+      <c r="E2324" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2324">
+        <v>3</v>
+      </c>
+      <c r="G2324" t="s">
+        <v>3084</v>
+      </c>
+    </row>
+    <row r="2325" spans="1:7">
+      <c r="A2325" t="s">
+        <v>2966</v>
+      </c>
+      <c r="B2325" t="s">
+        <v>3085</v>
+      </c>
+      <c r="C2325" t="s">
+        <v>753</v>
+      </c>
+      <c r="D2325">
+        <v>1350</v>
+      </c>
+      <c r="E2325" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2325">
+        <v>3</v>
+      </c>
+      <c r="G2325" t="s">
+        <v>3084</v>
+      </c>
+    </row>
+    <row r="2326" spans="1:7">
+      <c r="A2326" t="s">
+        <v>2686</v>
+      </c>
+      <c r="B2326" t="s">
+        <v>3086</v>
+      </c>
+      <c r="C2326" t="s">
+        <v>104</v>
+      </c>
+      <c r="D2326">
+        <v>250</v>
+      </c>
+      <c r="E2326" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2326">
+        <v>12</v>
+      </c>
+      <c r="G2326" t="s">
+        <v>3084</v>
+      </c>
+    </row>
+    <row r="2327" spans="1:7">
+      <c r="A2327" t="s">
+        <v>2704</v>
+      </c>
+      <c r="B2327" t="s">
+        <v>3087</v>
+      </c>
+      <c r="C2327" t="s">
+        <v>104</v>
+      </c>
+      <c r="D2327">
+        <v>350</v>
+      </c>
+      <c r="E2327" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2327">
+        <v>3</v>
+      </c>
+      <c r="G2327" t="s">
+        <v>3084</v>
+      </c>
+    </row>
+    <row r="2328" spans="1:7">
+      <c r="A2328" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2328" t="s">
+        <v>3088</v>
+      </c>
+      <c r="C2328" t="s">
+        <v>98</v>
+      </c>
+      <c r="D2328">
+        <v>1450</v>
+      </c>
+      <c r="E2328" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2328">
+        <v>5</v>
+      </c>
+      <c r="G2328" t="s">
+        <v>3089</v>
+      </c>
+    </row>
+    <row r="2329" spans="1:7">
+      <c r="A2329" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2329">
+        <v>7897056528137</v>
+      </c>
+      <c r="C2329" t="s">
+        <v>335</v>
+      </c>
+      <c r="D2329">
+        <v>180</v>
+      </c>
+      <c r="E2329" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2329">
+        <v>7</v>
+      </c>
+      <c r="G2329" t="s">
+        <v>3090</v>
+      </c>
+    </row>
+    <row r="2330" spans="1:7">
+      <c r="A2330" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2330" t="s">
+        <v>3091</v>
+      </c>
+      <c r="C2330" t="s">
+        <v>3062</v>
+      </c>
+      <c r="D2330">
+        <v>180</v>
+      </c>
+      <c r="E2330" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2330">
+        <v>4</v>
+      </c>
+      <c r="G2330" t="s">
+        <v>3090</v>
+      </c>
+    </row>
+    <row r="2331" spans="1:7">
+      <c r="A2331" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2331" t="s">
+        <v>3092</v>
+      </c>
+      <c r="C2331" t="s">
+        <v>2939</v>
+      </c>
+      <c r="D2331">
+        <v>150</v>
+      </c>
+      <c r="E2331" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2331">
+        <v>1</v>
+      </c>
+      <c r="G2331" t="s">
+        <v>3090</v>
+      </c>
+    </row>
+    <row r="2332" spans="1:7">
+      <c r="A2332" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2332" t="s">
+        <v>3093</v>
+      </c>
+      <c r="C2332" t="s">
+        <v>3062</v>
+      </c>
+      <c r="D2332">
+        <v>170</v>
+      </c>
+      <c r="E2332" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2332">
+        <v>1</v>
+      </c>
+      <c r="G2332" t="s">
+        <v>3090</v>
+      </c>
+    </row>
+    <row r="2333" spans="1:7">
+      <c r="A2333" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2333">
+        <v>9906101016012</v>
+      </c>
+      <c r="C2333" t="s">
+        <v>3094</v>
+      </c>
+      <c r="D2333">
+        <v>180</v>
+      </c>
+      <c r="E2333" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2333">
+        <v>1</v>
+      </c>
+      <c r="G2333" t="s">
+        <v>3090</v>
+      </c>
+    </row>
+    <row r="2334" spans="1:7">
+      <c r="A2334" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2334">
+        <v>7898541344652</v>
+      </c>
+      <c r="C2334" t="s">
+        <v>278</v>
+      </c>
+      <c r="D2334">
+        <v>250</v>
+      </c>
+      <c r="E2334" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2334">
+        <v>3</v>
+      </c>
+      <c r="G2334" t="s">
+        <v>3090</v>
+      </c>
+    </row>
+    <row r="2335" spans="1:7">
+      <c r="A2335" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2335">
+        <v>4549250013546</v>
+      </c>
+      <c r="C2335" t="s">
+        <v>3037</v>
+      </c>
+      <c r="D2335">
+        <v>400</v>
+      </c>
+      <c r="E2335" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2335">
+        <v>12</v>
+      </c>
+      <c r="G2335" t="s">
+        <v>3090</v>
+      </c>
+    </row>
+    <row r="2336" spans="1:7">
+      <c r="A2336" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2336" t="s">
+        <v>3095</v>
+      </c>
+      <c r="C2336" t="s">
+        <v>3096</v>
+      </c>
+      <c r="D2336">
+        <v>320</v>
+      </c>
+      <c r="E2336" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2336">
+        <v>2</v>
+      </c>
+      <c r="G2336" t="s">
+        <v>3090</v>
+      </c>
+    </row>
+    <row r="2337" spans="1:7">
+      <c r="A2337" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2337" t="s">
+        <v>3097</v>
+      </c>
+      <c r="C2337" t="s">
+        <v>2939</v>
+      </c>
+      <c r="D2337">
+        <v>580</v>
+      </c>
+      <c r="E2337" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2337">
+        <v>5</v>
+      </c>
+      <c r="G2337" t="s">
+        <v>3090</v>
+      </c>
+    </row>
+    <row r="2338" spans="1:7">
+      <c r="A2338" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2338">
+        <v>7450076031065</v>
+      </c>
+      <c r="C2338" t="s">
+        <v>2939</v>
+      </c>
+      <c r="D2338">
+        <v>350</v>
+      </c>
+      <c r="E2338" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2338">
+        <v>4</v>
+      </c>
+      <c r="G2338" t="s">
+        <v>3090</v>
+      </c>
+    </row>
+    <row r="2339" spans="1:7">
+      <c r="A2339" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2339" t="s">
+        <v>3098</v>
+      </c>
+      <c r="C2339" t="s">
+        <v>3037</v>
+      </c>
+      <c r="D2339">
+        <v>450</v>
+      </c>
+      <c r="E2339" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2339">
+        <v>7</v>
+      </c>
+      <c r="G2339" t="s">
+        <v>3090</v>
+      </c>
+    </row>
+    <row r="2340" spans="1:7">
+      <c r="A2340" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2340" t="s">
+        <v>3099</v>
+      </c>
+      <c r="C2340" t="s">
+        <v>3066</v>
+      </c>
+      <c r="D2340">
+        <v>480</v>
+      </c>
+      <c r="E2340" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2340">
+        <v>12</v>
+      </c>
+      <c r="G2340" t="s">
+        <v>3090</v>
+      </c>
+    </row>
+    <row r="2341" spans="1:7">
+      <c r="A2341" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2341">
+        <v>4549250016981</v>
+      </c>
+      <c r="C2341" t="s">
+        <v>3037</v>
+      </c>
+      <c r="D2341">
+        <v>550</v>
+      </c>
+      <c r="E2341" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2341">
+        <v>2</v>
+      </c>
+      <c r="G2341" t="s">
+        <v>3090</v>
+      </c>
+    </row>
+    <row r="2342" spans="1:7">
+      <c r="A2342" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2342" t="s">
+        <v>3100</v>
+      </c>
+      <c r="C2342" t="s">
+        <v>2847</v>
+      </c>
+      <c r="D2342">
+        <v>300</v>
+      </c>
+      <c r="E2342" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2342">
+        <v>3</v>
+      </c>
+      <c r="G2342" t="s">
+        <v>3101</v>
+      </c>
+    </row>
+    <row r="2343" spans="1:7">
+      <c r="A2343" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2343" t="s">
+        <v>3102</v>
+      </c>
+      <c r="C2343" t="s">
+        <v>2939</v>
+      </c>
+      <c r="D2343">
+        <v>160</v>
+      </c>
+      <c r="E2343" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2343">
+        <v>2</v>
+      </c>
+      <c r="G2343" t="s">
+        <v>3101</v>
+      </c>
+    </row>
+    <row r="2344" spans="1:7">
+      <c r="A2344" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2344" t="s">
+        <v>3103</v>
+      </c>
+      <c r="C2344" t="s">
+        <v>3066</v>
+      </c>
+      <c r="D2344">
+        <v>295</v>
+      </c>
+      <c r="E2344" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2344">
+        <v>6</v>
+      </c>
+      <c r="G2344" t="s">
+        <v>3101</v>
+      </c>
+    </row>
+    <row r="2345" spans="1:7">
+      <c r="A2345" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2345">
+        <v>4549250142437</v>
+      </c>
+      <c r="C2345" t="s">
+        <v>3037</v>
+      </c>
+      <c r="D2345">
+        <v>260</v>
+      </c>
+      <c r="E2345" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2345">
+        <v>2</v>
+      </c>
+      <c r="G2345" t="s">
+        <v>3101</v>
+      </c>
+    </row>
+    <row r="2346" spans="1:7">
+      <c r="A2346" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2346" t="s">
+        <v>3104</v>
+      </c>
+      <c r="C2346" t="s">
+        <v>760</v>
+      </c>
+      <c r="D2346">
+        <v>1500</v>
+      </c>
+      <c r="E2346" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2346">
+        <v>3</v>
+      </c>
+      <c r="G2346" t="s">
+        <v>3105</v>
+      </c>
+    </row>
+    <row r="2347" spans="1:7">
+      <c r="A2347" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2347" t="s">
+        <v>3106</v>
+      </c>
+      <c r="C2347" t="s">
+        <v>459</v>
+      </c>
+      <c r="D2347">
+        <v>1600</v>
+      </c>
+      <c r="E2347" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2347">
+        <v>2</v>
+      </c>
+      <c r="G2347" t="s">
+        <v>3105</v>
+      </c>
+    </row>
+    <row r="2348" spans="1:7">
+      <c r="A2348" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2348" t="s">
+        <v>3107</v>
+      </c>
+      <c r="C2348" t="s">
+        <v>753</v>
+      </c>
+      <c r="D2348">
+        <v>1750</v>
+      </c>
+      <c r="E2348" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2348">
+        <v>2</v>
+      </c>
+      <c r="G2348" t="s">
+        <v>3105</v>
+      </c>
+    </row>
+    <row r="2349" spans="1:7">
+      <c r="A2349" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2349">
+        <v>4549250745874</v>
+      </c>
+      <c r="C2349" t="s">
+        <v>3037</v>
+      </c>
+      <c r="D2349">
+        <v>200</v>
+      </c>
+      <c r="E2349" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2349">
+        <v>5</v>
+      </c>
+      <c r="G2349" t="s">
+        <v>3108</v>
+      </c>
+    </row>
+    <row r="2350" spans="1:7">
+      <c r="A2350" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2350">
+        <v>4549250318054</v>
+      </c>
+      <c r="C2350" t="s">
+        <v>3037</v>
+      </c>
+      <c r="D2350">
+        <v>450</v>
+      </c>
+      <c r="E2350" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2350">
+        <v>20</v>
+      </c>
+      <c r="G2350" t="s">
+        <v>3108</v>
+      </c>
+    </row>
+    <row r="2351" spans="1:7">
+      <c r="A2351" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2351" t="s">
+        <v>3109</v>
+      </c>
+      <c r="C2351" t="s">
+        <v>3110</v>
+      </c>
+      <c r="D2351">
+        <v>320</v>
+      </c>
+      <c r="E2351" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2351">
+        <v>3</v>
+      </c>
+      <c r="G2351" t="s">
+        <v>3108</v>
+      </c>
+    </row>
+    <row r="2352" spans="1:7">
+      <c r="A2352" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2352" t="s">
+        <v>3111</v>
+      </c>
+      <c r="C2352" t="s">
+        <v>3055</v>
+      </c>
+      <c r="D2352">
+        <v>300</v>
+      </c>
+      <c r="E2352" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2352">
+        <v>4</v>
+      </c>
+      <c r="G2352" t="s">
+        <v>3108</v>
+      </c>
+    </row>
+    <row r="2353" spans="1:7">
+      <c r="A2353" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2353">
+        <v>4549250013584</v>
+      </c>
+      <c r="C2353" t="s">
+        <v>3037</v>
+      </c>
+      <c r="D2353">
+        <v>450</v>
+      </c>
+      <c r="E2353" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2353">
+        <v>3</v>
+      </c>
+      <c r="G2353" t="s">
+        <v>3108</v>
+      </c>
+    </row>
+    <row r="2354" spans="1:7">
+      <c r="A2354" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2354" t="s">
+        <v>3112</v>
+      </c>
+      <c r="C2354" t="s">
+        <v>2939</v>
+      </c>
+      <c r="D2354">
+        <v>320</v>
+      </c>
+      <c r="E2354" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2354">
+        <v>1</v>
+      </c>
+      <c r="G2354" t="s">
+        <v>3108</v>
+      </c>
+    </row>
+    <row r="2355" spans="1:7">
+      <c r="A2355" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2355" t="s">
+        <v>3113</v>
+      </c>
+      <c r="C2355" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2355">
+        <v>300</v>
+      </c>
+      <c r="E2355" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2355">
+        <v>1</v>
+      </c>
+      <c r="G2355" t="s">
+        <v>3108</v>
+      </c>
+    </row>
+    <row r="2356" spans="1:7">
+      <c r="A2356" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2356" t="s">
+        <v>3114</v>
+      </c>
+      <c r="C2356" t="s">
+        <v>459</v>
+      </c>
+      <c r="D2356">
+        <v>2600</v>
+      </c>
+      <c r="E2356" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2356">
+        <v>3</v>
+      </c>
+      <c r="G2356" t="s">
+        <v>3108</v>
+      </c>
+    </row>
+    <row r="2357" spans="1:7">
+      <c r="A2357" t="s">
+        <v>736</v>
+      </c>
+      <c r="B2357" t="s">
+        <v>3115</v>
+      </c>
+      <c r="C2357" t="s">
+        <v>459</v>
+      </c>
+      <c r="D2357">
+        <v>1200</v>
+      </c>
+      <c r="E2357" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2357">
+        <v>3</v>
+      </c>
+      <c r="G2357" t="s">
+        <v>3108</v>
+      </c>
+    </row>
+    <row r="2358" spans="1:7">
+      <c r="A2358" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2358" t="s">
+        <v>3116</v>
+      </c>
+      <c r="C2358" t="s">
+        <v>3037</v>
+      </c>
+      <c r="D2358">
+        <v>1200</v>
+      </c>
+      <c r="E2358" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2358">
+        <v>3</v>
+      </c>
+      <c r="G2358" t="s">
+        <v>3117</v>
+      </c>
+    </row>
+    <row r="2359" spans="1:7">
+      <c r="A2359" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2359" t="s">
+        <v>3118</v>
+      </c>
+      <c r="C2359" t="s">
+        <v>3055</v>
+      </c>
+      <c r="D2359">
+        <v>900</v>
+      </c>
+      <c r="E2359" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2359">
+        <v>1</v>
+      </c>
+      <c r="G2359" t="s">
+        <v>3117</v>
+      </c>
+    </row>
+    <row r="2360" spans="1:7">
+      <c r="A2360" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2360" t="s">
+        <v>3119</v>
+      </c>
+      <c r="C2360" t="s">
+        <v>2939</v>
+      </c>
+      <c r="D2360">
+        <v>950</v>
+      </c>
+      <c r="E2360" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2360">
+        <v>4</v>
+      </c>
+      <c r="G2360" t="s">
+        <v>3117</v>
+      </c>
+    </row>
+    <row r="2361" spans="1:7">
+      <c r="A2361" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2361">
+        <v>4549250155475</v>
+      </c>
+      <c r="C2361" t="s">
+        <v>3037</v>
+      </c>
+      <c r="D2361">
+        <v>300</v>
+      </c>
+      <c r="E2361" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2361">
+        <v>24</v>
+      </c>
+      <c r="G2361" t="s">
+        <v>3117</v>
+      </c>
+    </row>
+    <row r="2362" spans="1:7">
+      <c r="A2362" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2362" t="s">
+        <v>3120</v>
+      </c>
+      <c r="C2362" t="s">
+        <v>3066</v>
+      </c>
+      <c r="D2362">
+        <v>280</v>
+      </c>
+      <c r="E2362" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2362">
+        <v>2</v>
+      </c>
+      <c r="G2362" t="s">
+        <v>3117</v>
+      </c>
+    </row>
+    <row r="2363" spans="1:7">
+      <c r="A2363" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2363" t="s">
+        <v>3121</v>
+      </c>
+      <c r="C2363" t="s">
+        <v>3122</v>
+      </c>
+      <c r="D2363">
+        <v>120</v>
+      </c>
+      <c r="E2363" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2363">
+        <v>5</v>
+      </c>
+      <c r="G2363" t="s">
+        <v>3117</v>
+      </c>
+    </row>
+    <row r="2364" spans="1:7">
+      <c r="A2364" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2364" t="s">
+        <v>3123</v>
+      </c>
+      <c r="C2364" t="s">
+        <v>1580</v>
+      </c>
+      <c r="D2364">
+        <v>100</v>
+      </c>
+      <c r="E2364" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2364">
+        <v>1</v>
+      </c>
+      <c r="G2364" t="s">
+        <v>3117</v>
+      </c>
+    </row>
+    <row r="2365" spans="1:7">
+      <c r="A2365" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2365">
+        <v>4549250143052</v>
+      </c>
+      <c r="C2365" t="s">
+        <v>3037</v>
+      </c>
+      <c r="D2365">
+        <v>250</v>
+      </c>
+      <c r="E2365" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2365">
+        <v>1</v>
+      </c>
+      <c r="G2365" t="s">
+        <v>3117</v>
+      </c>
+    </row>
+    <row r="2366" spans="1:7">
+      <c r="A2366" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2366" t="s">
+        <v>3124</v>
+      </c>
+      <c r="C2366" t="s">
+        <v>3066</v>
+      </c>
+      <c r="D2366">
+        <v>300</v>
+      </c>
+      <c r="E2366" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2366">
+        <v>3</v>
+      </c>
+      <c r="G2366" t="s">
+        <v>3117</v>
+      </c>
+    </row>
+    <row r="2367" spans="1:7">
+      <c r="A2367" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2367" t="s">
+        <v>3125</v>
+      </c>
+      <c r="C2367" t="s">
+        <v>2939</v>
+      </c>
+      <c r="D2367">
+        <v>200</v>
+      </c>
+      <c r="E2367" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2367">
+        <v>1</v>
+      </c>
+      <c r="G2367" t="s">
+        <v>3117</v>
+      </c>
+    </row>
+    <row r="2368" spans="1:7">
+      <c r="A2368" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2368">
+        <v>4549250012211</v>
+      </c>
+      <c r="C2368" t="s">
+        <v>3037</v>
+      </c>
+      <c r="D2368">
+        <v>700</v>
+      </c>
+      <c r="E2368" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2368">
+        <v>2</v>
+      </c>
+      <c r="G2368" t="s">
+        <v>3117</v>
+      </c>
+    </row>
+    <row r="2369" spans="1:7">
+      <c r="A2369" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2369" t="s">
+        <v>3126</v>
+      </c>
+      <c r="C2369" t="s">
+        <v>2939</v>
+      </c>
+      <c r="D2369">
+        <v>450</v>
+      </c>
+      <c r="E2369" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2369">
+        <v>1</v>
+      </c>
+      <c r="G2369" t="s">
+        <v>3117</v>
+      </c>
+    </row>
+    <row r="2370" spans="1:7">
+      <c r="A2370" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2370">
+        <v>7898252655993</v>
+      </c>
+      <c r="C2370" t="s">
+        <v>278</v>
+      </c>
+      <c r="D2370">
+        <v>200</v>
+      </c>
+      <c r="E2370" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2370">
+        <v>4</v>
+      </c>
+      <c r="G2370" t="s">
+        <v>3117</v>
+      </c>
+    </row>
+    <row r="2371" spans="1:7">
+      <c r="A2371" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2371" t="s">
+        <v>3127</v>
+      </c>
+      <c r="C2371" t="s">
+        <v>3066</v>
+      </c>
+      <c r="D2371">
+        <v>650</v>
+      </c>
+      <c r="E2371" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2371">
+        <v>2</v>
+      </c>
+      <c r="G2371" t="s">
+        <v>3117</v>
+      </c>
+    </row>
+    <row r="2372" spans="1:7">
+      <c r="A2372" t="s">
+        <v>3128</v>
+      </c>
+      <c r="B2372">
+        <v>4549250168215</v>
+      </c>
+      <c r="C2372" t="s">
+        <v>3037</v>
+      </c>
+      <c r="D2372">
+        <v>490</v>
+      </c>
+      <c r="E2372" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2372">
+        <v>3</v>
+      </c>
+      <c r="G2372" t="s">
+        <v>3117</v>
+      </c>
+    </row>
+    <row r="2373" spans="1:7">
+      <c r="A2373" t="s">
+        <v>3129</v>
+      </c>
+      <c r="B2373">
+        <v>1234567</v>
+      </c>
+      <c r="C2373" t="s">
+        <v>98</v>
+      </c>
+      <c r="D2373">
+        <v>320</v>
+      </c>
+      <c r="E2373" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2373">
+        <v>14</v>
+      </c>
+      <c r="G2373" t="s">
+        <v>3117</v>
+      </c>
+    </row>
+    <row r="2374" spans="1:7">
+      <c r="A2374" t="s">
+        <v>3130</v>
+      </c>
+      <c r="B2374" t="s">
+        <v>3131</v>
+      </c>
+      <c r="C2374" t="s">
+        <v>760</v>
+      </c>
+      <c r="D2374">
+        <v>750</v>
+      </c>
+      <c r="E2374" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2374">
+        <v>3</v>
+      </c>
+      <c r="G2374" t="s">
+        <v>3117</v>
+      </c>
+    </row>
+    <row r="2375" spans="1:7">
+      <c r="A2375" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2375" t="s">
+        <v>3132</v>
+      </c>
+      <c r="C2375" t="s">
+        <v>3055</v>
+      </c>
+      <c r="D2375">
+        <v>650</v>
+      </c>
+      <c r="E2375" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2375">
+        <v>1</v>
+      </c>
+      <c r="G2375" t="s">
+        <v>3133</v>
+      </c>
+    </row>
+    <row r="2376" spans="1:7">
+      <c r="A2376" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2376" t="s">
+        <v>3134</v>
+      </c>
+      <c r="C2376" t="s">
+        <v>2939</v>
+      </c>
+      <c r="D2376">
+        <v>200</v>
+      </c>
+      <c r="E2376" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2376">
+        <v>2</v>
+      </c>
+      <c r="G2376" t="s">
+        <v>3133</v>
+      </c>
+    </row>
+    <row r="2377" spans="1:7">
+      <c r="A2377" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2377">
+        <v>4549250182310</v>
+      </c>
+      <c r="C2377" t="s">
+        <v>3037</v>
+      </c>
+      <c r="D2377">
+        <v>350</v>
+      </c>
+      <c r="E2377" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2377">
+        <v>4</v>
+      </c>
+      <c r="G2377" t="s">
+        <v>3133</v>
+      </c>
+    </row>
+    <row r="2378" spans="1:7">
+      <c r="A2378" t="s">
+        <v>3128</v>
+      </c>
+      <c r="B2378" t="s">
+        <v>3135</v>
+      </c>
+      <c r="C2378" t="s">
+        <v>3066</v>
+      </c>
+      <c r="D2378">
+        <v>1450</v>
+      </c>
+      <c r="E2378" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2378">
+        <v>1</v>
+      </c>
+      <c r="G2378" t="s">
+        <v>3133</v>
+      </c>
+    </row>
+    <row r="2379" spans="1:7">
+      <c r="A2379" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B2379">
+        <v>4549250016752</v>
+      </c>
+      <c r="C2379" t="s">
+        <v>3037</v>
+      </c>
+      <c r="D2379">
+        <v>280</v>
+      </c>
+      <c r="E2379" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2379">
+        <v>1</v>
+      </c>
+      <c r="G2379" t="s">
+        <v>3133</v>
       </c>
     </row>
   </sheetData>
